--- a/test_output/workflow_test/yield_table.xlsx
+++ b/test_output/workflow_test/yield_table.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,87 +417,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tpa</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>basal_area</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>qmd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>mean_dbh</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>top_height</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>mean_height</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ccf</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>sdi</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max_sdi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>relsdi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>merchantable_volume</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>board_feet</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>site_index</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>initial_tpa</t>
         </is>
@@ -520,25 +508,25 @@
         <v>400</v>
       </c>
       <c r="B2" t="n">
-        <v>0.55</v>
+        <v>0.02</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5029932303624048</v>
+        <v>0.09999999999999948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0439888878852403</v>
+        <v>0.4000000000000003</v>
       </c>
       <c r="H2" t="n">
-        <v>3.296607376825627</v>
+        <v>0.2466380007445908</v>
       </c>
       <c r="I2" t="n">
         <v>480</v>
@@ -550,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>74.89</v>
+        <v>74.64</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -572,40 +560,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82</v>
+        <v>0.02</v>
       </c>
       <c r="C3" t="n">
-        <v>2.880001614028414</v>
+        <v>0.1004999999999996</v>
       </c>
       <c r="D3" t="n">
-        <v>2.88</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>22.63763141941052</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>22.57</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.42049724280948</v>
+        <v>0.001720984272611824</v>
       </c>
       <c r="H3" t="n">
-        <v>53.43447605407996</v>
+        <v>0.2436478571314069</v>
       </c>
       <c r="I3" t="n">
         <v>480</v>
       </c>
       <c r="J3" t="n">
-        <v>1.113218251126666</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>257.94</v>
+        <v>73.14</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -627,40 +615,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B4" t="n">
-        <v>43.03</v>
+        <v>0.02</v>
       </c>
       <c r="C4" t="n">
-        <v>4.532739783743485</v>
+        <v>0.1033516461410689</v>
       </c>
       <c r="D4" t="n">
-        <v>4.53</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>36.11698406571623</v>
+        <v>2.85164614106908</v>
       </c>
       <c r="F4" t="n">
-        <v>36.06</v>
+        <v>2.85</v>
       </c>
       <c r="G4" t="n">
-        <v>2.365737714390702</v>
+        <v>0.001792176639788106</v>
       </c>
       <c r="H4" t="n">
-        <v>107.8425848164341</v>
+        <v>0.2509381713792228</v>
       </c>
       <c r="I4" t="n">
         <v>480</v>
       </c>
       <c r="J4" t="n">
-        <v>2.246720517009044</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>782.83</v>
+        <v>72.05</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -685,40 +673,40 @@
         <v>379</v>
       </c>
       <c r="B5" t="n">
-        <v>79.53</v>
+        <v>1.99</v>
       </c>
       <c r="C5" t="n">
-        <v>6.20270771802055</v>
+        <v>0.9803060858663998</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>48.38944971216294</v>
+        <v>8.147427260670293</v>
       </c>
       <c r="F5" t="n">
-        <v>48.33</v>
+        <v>8.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.482699896682445</v>
+        <v>0.1583147277944962</v>
       </c>
       <c r="H5" t="n">
-        <v>176.0889986076711</v>
+        <v>9.115379126914846</v>
       </c>
       <c r="I5" t="n">
         <v>480</v>
       </c>
       <c r="J5" t="n">
-        <v>3.668520804326481</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>1832.52</v>
+        <v>78.13</v>
       </c>
       <c r="M5" t="n">
-        <v>531.2168635285503</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -737,43 +725,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B6" t="n">
-        <v>117.55</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>7.611481095807586</v>
+        <v>2.059434669044244</v>
       </c>
       <c r="D6" t="n">
-        <v>7.61</v>
+        <v>2.06</v>
       </c>
       <c r="E6" t="n">
-        <v>58.15732951667125</v>
+        <v>16.34229117739838</v>
       </c>
       <c r="F6" t="n">
-        <v>58.09</v>
+        <v>16.34</v>
       </c>
       <c r="G6" t="n">
-        <v>4.542840461644659</v>
+        <v>0.6802696822937081</v>
       </c>
       <c r="H6" t="n">
-        <v>240.0495867628545</v>
+        <v>29.21406138265069</v>
       </c>
       <c r="I6" t="n">
         <v>480</v>
       </c>
       <c r="J6" t="n">
-        <v>5.00103305755947</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>3199.62</v>
+        <v>90.75</v>
       </c>
       <c r="M6" t="n">
-        <v>1305.435496376861</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -795,43 +783,43 @@
         <v>366</v>
       </c>
       <c r="B7" t="n">
-        <v>153.87</v>
+        <v>24.44</v>
       </c>
       <c r="C7" t="n">
-        <v>8.77964073800727</v>
+        <v>3.498737548829626</v>
       </c>
       <c r="D7" t="n">
-        <v>8.77</v>
+        <v>3.5</v>
       </c>
       <c r="E7" t="n">
-        <v>65.99379174143088</v>
+        <v>28.45893496954458</v>
       </c>
       <c r="F7" t="n">
-        <v>65.92</v>
+        <v>28.46</v>
       </c>
       <c r="G7" t="n">
-        <v>5.50542150900197</v>
+        <v>1.679198455137412</v>
       </c>
       <c r="H7" t="n">
-        <v>297.0032906374731</v>
+        <v>67.83578072923345</v>
       </c>
       <c r="I7" t="n">
         <v>480</v>
       </c>
       <c r="J7" t="n">
-        <v>6.187568554947356</v>
+        <v>1.41324543185903</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>4718.46</v>
+        <v>258.44</v>
       </c>
       <c r="M7" t="n">
-        <v>2255.788648062923</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>857.2149024383428</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -850,25 +838,25 @@
         <v>600</v>
       </c>
       <c r="B8" t="n">
-        <v>0.84</v>
+        <v>0.03</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5069569611518455</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0670273644462927</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H8" t="n">
-        <v>5.00760254150969</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I8" t="n">
         <v>480</v>
@@ -880,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>112.33</v>
+        <v>111.96</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -902,40 +890,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B9" t="n">
-        <v>26.86</v>
+        <v>0.03</v>
       </c>
       <c r="C9" t="n">
-        <v>2.879250984525404</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D9" t="n">
-        <v>2.88</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>22.63448719060483</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>22.57</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.140445646189204</v>
+        <v>0.002585866674919268</v>
       </c>
       <c r="H9" t="n">
-        <v>80.52487902137703</v>
+        <v>0.3660933363530567</v>
       </c>
       <c r="I9" t="n">
         <v>480</v>
       </c>
       <c r="J9" t="n">
-        <v>1.677601646278688</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>388.67</v>
+        <v>109.9</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -957,40 +945,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="B10" t="n">
-        <v>64.7</v>
+        <v>0.03</v>
       </c>
       <c r="C10" t="n">
-        <v>4.499332245904254</v>
+        <v>0.1033516333158758</v>
       </c>
       <c r="D10" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>36.0676306537212</v>
+        <v>2.851633315875424</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>2.85</v>
       </c>
       <c r="G10" t="n">
-        <v>3.578255957200619</v>
+        <v>0.002655763687921197</v>
       </c>
       <c r="H10" t="n">
-        <v>162.6298490643424</v>
+        <v>0.3718564907794852</v>
       </c>
       <c r="I10" t="n">
         <v>480</v>
       </c>
       <c r="J10" t="n">
-        <v>3.388121855507133</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>1177.2</v>
+        <v>106.77</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1012,43 +1000,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="B11" t="n">
-        <v>112.87</v>
+        <v>2.96</v>
       </c>
       <c r="C11" t="n">
-        <v>6.004488170164657</v>
+        <v>0.9802991934507943</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>0.98</v>
       </c>
       <c r="E11" t="n">
-        <v>48.24040554487912</v>
+        <v>8.147374919912409</v>
       </c>
       <c r="F11" t="n">
-        <v>48.17</v>
+        <v>8.15</v>
       </c>
       <c r="G11" t="n">
-        <v>5.049708471072671</v>
+        <v>0.2355890525400796</v>
       </c>
       <c r="H11" t="n">
-        <v>253.1429646709479</v>
+        <v>13.56468552223021</v>
       </c>
       <c r="I11" t="n">
         <v>480</v>
       </c>
       <c r="J11" t="n">
-        <v>5.273811763978083</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>2599.75</v>
+        <v>116.27</v>
       </c>
       <c r="M11" t="n">
-        <v>702.6849256051228</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1067,43 +1055,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="B12" t="n">
-        <v>159.99</v>
+        <v>12.83</v>
       </c>
       <c r="C12" t="n">
-        <v>7.199144773956875</v>
+        <v>2.05889884876796</v>
       </c>
       <c r="D12" t="n">
-        <v>7.19</v>
+        <v>2.06</v>
       </c>
       <c r="E12" t="n">
-        <v>57.88556544565979</v>
+        <v>16.33822217735833</v>
       </c>
       <c r="F12" t="n">
-        <v>57.82</v>
+        <v>16.34</v>
       </c>
       <c r="G12" t="n">
-        <v>6.384623223305535</v>
+        <v>1.022637503365814</v>
       </c>
       <c r="H12" t="n">
-        <v>334.0044763895795</v>
+        <v>43.92150118991381</v>
       </c>
       <c r="I12" t="n">
         <v>480</v>
       </c>
       <c r="J12" t="n">
-        <v>6.958426591449573</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>4346.11</v>
+        <v>136.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1650.139867739313</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1122,43 +1110,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="B13" t="n">
-        <v>200.85</v>
+        <v>35.94</v>
       </c>
       <c r="C13" t="n">
-        <v>8.145615514657084</v>
+        <v>3.496646576975184</v>
       </c>
       <c r="D13" t="n">
-        <v>8.130000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="E13" t="n">
-        <v>65.70990923717899</v>
+        <v>28.43095884604433</v>
       </c>
       <c r="F13" t="n">
-        <v>65.63</v>
+        <v>28.43</v>
       </c>
       <c r="G13" t="n">
-        <v>7.472414850748994</v>
+        <v>2.471329865196306</v>
       </c>
       <c r="H13" t="n">
-        <v>399.3244054012164</v>
+        <v>99.80442688903058</v>
       </c>
       <c r="I13" t="n">
         <v>480</v>
       </c>
       <c r="J13" t="n">
-        <v>8.319258445858676</v>
+        <v>2.07925889352147</v>
       </c>
       <c r="K13" t="n">
         <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>6147.03</v>
+        <v>379.66</v>
       </c>
       <c r="M13" t="n">
-        <v>2733.375523132395</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1180,25 +1168,25 @@
         <v>800</v>
       </c>
       <c r="B14" t="n">
-        <v>1.13</v>
+        <v>0.04</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5089808083405145</v>
+        <v>0.09999999999999921</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09008479865036262</v>
+        <v>0.8000000000000006</v>
       </c>
       <c r="H14" t="n">
-        <v>6.719635957851057</v>
+        <v>0.4932760014891795</v>
       </c>
       <c r="I14" t="n">
         <v>480</v>
@@ -1210,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>149.78</v>
+        <v>149.27</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1232,40 +1220,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B15" t="n">
-        <v>35.44</v>
+        <v>0.04</v>
       </c>
       <c r="C15" t="n">
-        <v>2.87880440719429</v>
+        <v>0.1004999999999993</v>
       </c>
       <c r="D15" t="n">
-        <v>2.88</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>22.63134037451144</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>22.56</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.824223688611342</v>
+        <v>0.003450749077226701</v>
       </c>
       <c r="H15" t="n">
-        <v>106.2555387603716</v>
+        <v>0.4885388155747066</v>
       </c>
       <c r="I15" t="n">
         <v>480</v>
       </c>
       <c r="J15" t="n">
-        <v>2.213657057507742</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>512.8200000000001</v>
+        <v>146.66</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1287,40 +1275,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="B16" t="n">
-        <v>82.17</v>
+        <v>0.05</v>
       </c>
       <c r="C16" t="n">
-        <v>4.440730870078688</v>
+        <v>0.1033516204906826</v>
       </c>
       <c r="D16" t="n">
-        <v>4.44</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>36.02060164399775</v>
+        <v>2.851620490681768</v>
       </c>
       <c r="F16" t="n">
-        <v>35.96</v>
+        <v>2.85</v>
       </c>
       <c r="G16" t="n">
-        <v>4.592564083581935</v>
+        <v>0.003612209154555211</v>
       </c>
       <c r="H16" t="n">
-        <v>207.6145357736578</v>
+        <v>0.5057767346258768</v>
       </c>
       <c r="I16" t="n">
         <v>480</v>
       </c>
       <c r="J16" t="n">
-        <v>4.325302828617871</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>1496.97</v>
+        <v>145.22</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1342,43 +1330,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>746</v>
+        <v>764</v>
       </c>
       <c r="B17" t="n">
-        <v>138.43</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>5.832786720597488</v>
+        <v>0.9802918927119281</v>
       </c>
       <c r="D17" t="n">
-        <v>5.83</v>
+        <v>0.98</v>
       </c>
       <c r="E17" t="n">
-        <v>48.11285580735111</v>
+        <v>8.147319478362187</v>
       </c>
       <c r="F17" t="n">
-        <v>48.05</v>
+        <v>8.15</v>
       </c>
       <c r="G17" t="n">
-        <v>6.314705951659139</v>
+        <v>0.3191265163359464</v>
       </c>
       <c r="H17" t="n">
-        <v>314.029149025472</v>
+        <v>18.37463805587524</v>
       </c>
       <c r="I17" t="n">
         <v>480</v>
       </c>
       <c r="J17" t="n">
-        <v>6.542273938030666</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>3188.06</v>
+        <v>157.5</v>
       </c>
       <c r="M17" t="n">
-        <v>804.6620711348208</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1397,43 +1385,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>728</v>
+        <v>751</v>
       </c>
       <c r="B18" t="n">
-        <v>188.66</v>
+        <v>17.35</v>
       </c>
       <c r="C18" t="n">
-        <v>6.893045737299057</v>
+        <v>2.058319809253634</v>
       </c>
       <c r="D18" t="n">
-        <v>6.88</v>
+        <v>2.06</v>
       </c>
       <c r="E18" t="n">
-        <v>57.72862847412209</v>
+        <v>16.33382497196874</v>
       </c>
       <c r="F18" t="n">
-        <v>57.66</v>
+        <v>16.33</v>
       </c>
       <c r="G18" t="n">
-        <v>7.725540930150117</v>
+        <v>1.38300692717094</v>
       </c>
       <c r="H18" t="n">
-        <v>400.6648938974932</v>
+        <v>59.40569309343856</v>
       </c>
       <c r="I18" t="n">
         <v>480</v>
       </c>
       <c r="J18" t="n">
-        <v>8.34718528953111</v>
+        <v>1.237618606113303</v>
       </c>
       <c r="K18" t="n">
         <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>5122.52</v>
+        <v>184.39</v>
       </c>
       <c r="M18" t="n">
-        <v>1827.128041971221</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1452,43 +1440,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>703</v>
+        <v>735</v>
       </c>
       <c r="B19" t="n">
-        <v>228.6</v>
+        <v>48.95</v>
       </c>
       <c r="C19" t="n">
-        <v>7.721376361883657</v>
+        <v>3.494413232070908</v>
       </c>
       <c r="D19" t="n">
-        <v>7.7</v>
+        <v>3.49</v>
       </c>
       <c r="E19" t="n">
-        <v>65.54926770875156</v>
+        <v>28.40135054936943</v>
       </c>
       <c r="F19" t="n">
-        <v>65.47</v>
+        <v>28.4</v>
       </c>
       <c r="G19" t="n">
-        <v>8.756287873783563</v>
+        <v>3.367683027997437</v>
       </c>
       <c r="H19" t="n">
-        <v>464.2002322225469</v>
+        <v>135.9574556048509</v>
       </c>
       <c r="I19" t="n">
         <v>480</v>
       </c>
       <c r="J19" t="n">
-        <v>9.67083817130306</v>
+        <v>2.832446991767727</v>
       </c>
       <c r="K19" t="n">
         <v>25</v>
       </c>
       <c r="L19" t="n">
-        <v>6992.7</v>
+        <v>516.34</v>
       </c>
       <c r="M19" t="n">
-        <v>2933.147096771715</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1510,25 +1498,25 @@
         <v>400</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5046378119998589</v>
+        <v>0.09999999999999948</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04427700939220103</v>
+        <v>0.4000000000000003</v>
       </c>
       <c r="H20" t="n">
-        <v>3.31392405964298</v>
+        <v>0.2466380007445908</v>
       </c>
       <c r="I20" t="n">
         <v>480</v>
@@ -1540,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>74.89</v>
+        <v>74.64</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1562,40 +1550,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B21" t="n">
-        <v>20.27</v>
+        <v>0.02</v>
       </c>
       <c r="C21" t="n">
-        <v>3.083123131336057</v>
+        <v>0.1004999999999996</v>
       </c>
       <c r="D21" t="n">
-        <v>3.08</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>24.18694215578868</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="n">
-        <v>24.12</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.572180608195864</v>
+        <v>0.00175171613462275</v>
       </c>
       <c r="H21" t="n">
-        <v>59.15713095039462</v>
+        <v>0.2479987117230391</v>
       </c>
       <c r="I21" t="n">
         <v>480</v>
       </c>
       <c r="J21" t="n">
-        <v>1.232440228133221</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>297.04</v>
+        <v>74.45</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1617,40 +1605,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B22" t="n">
-        <v>47.82</v>
+        <v>0.02</v>
       </c>
       <c r="C22" t="n">
-        <v>4.790706192689362</v>
+        <v>0.1034308528745656</v>
       </c>
       <c r="D22" t="n">
-        <v>4.79</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>38.59200293448766</v>
+        <v>2.930852874565874</v>
       </c>
       <c r="F22" t="n">
-        <v>38.52</v>
+        <v>2.93</v>
       </c>
       <c r="G22" t="n">
-        <v>2.517082980159323</v>
+        <v>0.001832125183849257</v>
       </c>
       <c r="H22" t="n">
-        <v>117.2477776726247</v>
+        <v>0.2564540970666321</v>
       </c>
       <c r="I22" t="n">
         <v>480</v>
       </c>
       <c r="J22" t="n">
-        <v>2.442662034846348</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>10</v>
       </c>
       <c r="L22" t="n">
-        <v>915.6</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1672,43 +1660,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="B23" t="n">
-        <v>84.18000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="C23" t="n">
-        <v>6.458791158755397</v>
+        <v>1.025951747419416</v>
       </c>
       <c r="D23" t="n">
-        <v>6.46</v>
+        <v>1.03</v>
       </c>
       <c r="E23" t="n">
-        <v>51.73604601077729</v>
+        <v>8.494058784148685</v>
       </c>
       <c r="F23" t="n">
-        <v>51.66</v>
+        <v>8.49</v>
       </c>
       <c r="G23" t="n">
-        <v>3.591538273882156</v>
+        <v>0.1761462133477603</v>
       </c>
       <c r="H23" t="n">
-        <v>183.4401799087207</v>
+        <v>9.96137893149371</v>
       </c>
       <c r="I23" t="n">
         <v>480</v>
       </c>
       <c r="J23" t="n">
-        <v>3.821670414765014</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>2062.66</v>
+        <v>10.94</v>
       </c>
       <c r="M23" t="n">
-        <v>651.7492909102045</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1727,43 +1715,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B24" t="n">
-        <v>122.96</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>7.869787226042682</v>
+        <v>2.170529568925843</v>
       </c>
       <c r="D24" t="n">
-        <v>7.86</v>
+        <v>2.17</v>
       </c>
       <c r="E24" t="n">
-        <v>62.20395276874774</v>
+        <v>17.18875143379408</v>
       </c>
       <c r="F24" t="n">
-        <v>62.13</v>
+        <v>17.19</v>
       </c>
       <c r="G24" t="n">
-        <v>4.663810605731426</v>
+        <v>0.7740730082016665</v>
       </c>
       <c r="H24" t="n">
-        <v>247.8118007372056</v>
+        <v>32.55965233066233</v>
       </c>
       <c r="I24" t="n">
         <v>480</v>
       </c>
       <c r="J24" t="n">
-        <v>5.162745848691785</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>3569.7</v>
+        <v>108.79</v>
       </c>
       <c r="M24" t="n">
-        <v>1521.744597152295</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1782,46 +1770,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="B25" t="n">
-        <v>159.08</v>
+        <v>27.84</v>
       </c>
       <c r="C25" t="n">
-        <v>9.03871189131738</v>
+        <v>3.694010326577089</v>
       </c>
       <c r="D25" t="n">
-        <v>9.029999999999999</v>
+        <v>3.69</v>
       </c>
       <c r="E25" t="n">
-        <v>70.61172663898297</v>
+        <v>30.45772968689101</v>
       </c>
       <c r="F25" t="n">
-        <v>70.53</v>
+        <v>30.46</v>
       </c>
       <c r="G25" t="n">
-        <v>5.608394827028722</v>
+        <v>1.820369869050002</v>
       </c>
       <c r="H25" t="n">
-        <v>303.5422985133637</v>
+        <v>75.63208290267347</v>
       </c>
       <c r="I25" t="n">
         <v>480</v>
       </c>
       <c r="J25" t="n">
-        <v>6.323797885695078</v>
+        <v>1.575668393805697</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>5210.08</v>
+        <v>320.52</v>
       </c>
       <c r="M25" t="n">
-        <v>2564.185921973962</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1820.355440779989</v>
+        <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1840,25 +1828,25 @@
         <v>600</v>
       </c>
       <c r="B26" t="n">
-        <v>0.84</v>
+        <v>0.03</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5069303292016513</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06702032233944388</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H26" t="n">
-        <v>5.007180330197106</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I26" t="n">
         <v>480</v>
@@ -1870,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>112.33</v>
+        <v>111.96</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1895,37 +1883,37 @@
         <v>589</v>
       </c>
       <c r="B27" t="n">
-        <v>30.52</v>
+        <v>0.03</v>
       </c>
       <c r="C27" t="n">
-        <v>3.082442606017842</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D27" t="n">
-        <v>3.08</v>
+        <v>0.1</v>
       </c>
       <c r="E27" t="n">
-        <v>24.18361595347733</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
-        <v>24.11</v>
+        <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>2.367793274934866</v>
+        <v>0.002585866674919268</v>
       </c>
       <c r="H27" t="n">
-        <v>89.08237109422427</v>
+        <v>0.3660933363530567</v>
       </c>
       <c r="I27" t="n">
         <v>480</v>
       </c>
       <c r="J27" t="n">
-        <v>1.855882731129672</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>447.24</v>
+        <v>109.9</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1947,40 +1935,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B28" t="n">
-        <v>70.56999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="C28" t="n">
-        <v>4.735490538527365</v>
+        <v>0.1034308400884663</v>
       </c>
       <c r="D28" t="n">
-        <v>4.74</v>
+        <v>0.1</v>
       </c>
       <c r="E28" t="n">
-        <v>38.53269413804813</v>
+        <v>2.930840088466014</v>
       </c>
       <c r="F28" t="n">
-        <v>38.46</v>
+        <v>2.93</v>
       </c>
       <c r="G28" t="n">
-        <v>3.748279699054601</v>
+        <v>0.002697036405857211</v>
       </c>
       <c r="H28" t="n">
-        <v>173.8347491400995</v>
+        <v>0.3775211847373399</v>
       </c>
       <c r="I28" t="n">
         <v>480</v>
       </c>
       <c r="J28" t="n">
-        <v>3.621557273752072</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>10</v>
       </c>
       <c r="L28" t="n">
-        <v>1351.79</v>
+        <v>108.26</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2005,40 +1993,40 @@
         <v>568</v>
       </c>
       <c r="B29" t="n">
-        <v>120.47</v>
+        <v>3.26</v>
       </c>
       <c r="C29" t="n">
-        <v>6.23588553067743</v>
+        <v>1.025944626510973</v>
       </c>
       <c r="D29" t="n">
-        <v>6.23</v>
+        <v>1.03</v>
       </c>
       <c r="E29" t="n">
-        <v>51.56462471523944</v>
+        <v>8.49400470822429</v>
       </c>
       <c r="F29" t="n">
-        <v>51.49</v>
+        <v>8.49</v>
       </c>
       <c r="G29" t="n">
-        <v>5.256511000319412</v>
+        <v>0.2598692475872837</v>
       </c>
       <c r="H29" t="n">
-        <v>266.1704516264015</v>
+        <v>14.69610442244491</v>
       </c>
       <c r="I29" t="n">
         <v>480</v>
       </c>
       <c r="J29" t="n">
-        <v>5.545217742216697</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>15</v>
       </c>
       <c r="L29" t="n">
-        <v>2949.36</v>
+        <v>16.14</v>
       </c>
       <c r="M29" t="n">
-        <v>871.451231300169</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2057,43 +2045,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B30" t="n">
-        <v>168.24</v>
+        <v>14.2</v>
       </c>
       <c r="C30" t="n">
-        <v>7.421732841624435</v>
+        <v>2.169915077558399</v>
       </c>
       <c r="D30" t="n">
-        <v>7.41</v>
+        <v>2.17</v>
       </c>
       <c r="E30" t="n">
-        <v>61.89109027027713</v>
+        <v>17.18408057658255</v>
       </c>
       <c r="F30" t="n">
-        <v>61.81</v>
+        <v>17.18</v>
       </c>
       <c r="G30" t="n">
-        <v>6.594945834366238</v>
+        <v>1.131799029710082</v>
       </c>
       <c r="H30" t="n">
-        <v>347.0156496340515</v>
+        <v>47.61192326640829</v>
       </c>
       <c r="I30" t="n">
         <v>480</v>
       </c>
       <c r="J30" t="n">
-        <v>7.229492700709407</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>20</v>
       </c>
       <c r="L30" t="n">
-        <v>4871.72</v>
+        <v>159.02</v>
       </c>
       <c r="M30" t="n">
-        <v>1936.158887499104</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2112,46 +2100,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B31" t="n">
-        <v>208.6</v>
+        <v>40.57</v>
       </c>
       <c r="C31" t="n">
-        <v>8.354073179750159</v>
+        <v>3.690878547540833</v>
       </c>
       <c r="D31" t="n">
-        <v>8.34</v>
+        <v>3.69</v>
       </c>
       <c r="E31" t="n">
-        <v>70.29313464835813</v>
+        <v>30.42623166274114</v>
       </c>
       <c r="F31" t="n">
-        <v>70.20999999999999</v>
+        <v>30.43</v>
       </c>
       <c r="G31" t="n">
-        <v>7.655771373807723</v>
+        <v>2.655063750744965</v>
       </c>
       <c r="H31" t="n">
-        <v>410.6078900211617</v>
+        <v>110.2645472696994</v>
       </c>
       <c r="I31" t="n">
         <v>480</v>
       </c>
       <c r="J31" t="n">
-        <v>8.554331042107535</v>
+        <v>2.297178068118737</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>6816.2</v>
+        <v>466.54</v>
       </c>
       <c r="M31" t="n">
-        <v>3122.218744743187</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>554.6286189710958</v>
+        <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2170,25 +2158,25 @@
         <v>800</v>
       </c>
       <c r="B32" t="n">
-        <v>1.14</v>
+        <v>0.04</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5121165017110929</v>
+        <v>0.09999999999999921</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0.09119819403805228</v>
+        <v>0.8000000000000006</v>
       </c>
       <c r="H32" t="n">
-        <v>6.786203253842378</v>
+        <v>0.4932760014891795</v>
       </c>
       <c r="I32" t="n">
         <v>480</v>
@@ -2200,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>149.79</v>
+        <v>149.27</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2222,40 +2210,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B33" t="n">
-        <v>40.77</v>
+        <v>0.04</v>
       </c>
       <c r="C33" t="n">
-        <v>3.081720772929349</v>
+        <v>0.1004999999999993</v>
       </c>
       <c r="D33" t="n">
-        <v>3.08</v>
+        <v>0.1</v>
       </c>
       <c r="E33" t="n">
-        <v>24.1800799474032</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>24.11</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>3.163008393817661</v>
+        <v>0.003459529609229822</v>
       </c>
       <c r="H33" t="n">
-        <v>118.9838331981389</v>
+        <v>0.4897819168866016</v>
       </c>
       <c r="I33" t="n">
         <v>480</v>
       </c>
       <c r="J33" t="n">
-        <v>2.47882985829456</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>597.27</v>
+        <v>147.03</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2277,40 +2265,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="B34" t="n">
-        <v>92.45999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="C34" t="n">
-        <v>4.661939025022103</v>
+        <v>0.1034308266967094</v>
       </c>
       <c r="D34" t="n">
-        <v>4.66</v>
+        <v>0.1</v>
       </c>
       <c r="E34" t="n">
-        <v>38.47322905877403</v>
+        <v>2.930826696708791</v>
       </c>
       <c r="F34" t="n">
-        <v>38.4</v>
+        <v>2.93</v>
       </c>
       <c r="G34" t="n">
-        <v>4.971125870287199</v>
+        <v>0.003594497589421317</v>
       </c>
       <c r="H34" t="n">
-        <v>229.1627250508561</v>
+        <v>0.5031445088941232</v>
       </c>
       <c r="I34" t="n">
         <v>480</v>
       </c>
       <c r="J34" t="n">
-        <v>4.774223438559503</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>10</v>
       </c>
       <c r="L34" t="n">
-        <v>1773.01</v>
+        <v>144.29</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2332,43 +2320,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="B35" t="n">
-        <v>151.58</v>
+        <v>4.32</v>
       </c>
       <c r="C35" t="n">
-        <v>6.015482489013594</v>
+        <v>1.025937207202426</v>
       </c>
       <c r="D35" t="n">
-        <v>6.01</v>
+        <v>1.03</v>
       </c>
       <c r="E35" t="n">
-        <v>51.39714075803821</v>
+        <v>8.493948366260284</v>
       </c>
       <c r="F35" t="n">
-        <v>51.32</v>
+        <v>8.49</v>
       </c>
       <c r="G35" t="n">
-        <v>6.771948002534098</v>
+        <v>0.3440472671475687</v>
       </c>
       <c r="H35" t="n">
-        <v>339.695911172372</v>
+        <v>19.45658847384946</v>
       </c>
       <c r="I35" t="n">
         <v>480</v>
       </c>
       <c r="J35" t="n">
-        <v>7.076998149424417</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>15</v>
       </c>
       <c r="L35" t="n">
-        <v>3709.25</v>
+        <v>21.37</v>
       </c>
       <c r="M35" t="n">
-        <v>1015.800267069433</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2387,43 +2375,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="B36" t="n">
-        <v>202.65</v>
+        <v>18.97</v>
       </c>
       <c r="C36" t="n">
-        <v>7.029144987446497</v>
+        <v>2.169296893691979</v>
       </c>
       <c r="D36" t="n">
-        <v>7.02</v>
+        <v>2.17</v>
       </c>
       <c r="E36" t="n">
-        <v>61.7180829594423</v>
+        <v>17.1793815677805</v>
       </c>
       <c r="F36" t="n">
-        <v>61.63</v>
+        <v>17.18</v>
       </c>
       <c r="G36" t="n">
-        <v>8.200434120019647</v>
+        <v>1.511614809474693</v>
       </c>
       <c r="H36" t="n">
-        <v>427.0673354673544</v>
+        <v>63.59696994826867</v>
       </c>
       <c r="I36" t="n">
         <v>480</v>
       </c>
       <c r="J36" t="n">
-        <v>8.897236155569884</v>
+        <v>1.324936873922264</v>
       </c>
       <c r="K36" t="n">
         <v>20</v>
       </c>
       <c r="L36" t="n">
-        <v>5866.43</v>
+        <v>212.33</v>
       </c>
       <c r="M36" t="n">
-        <v>2166.525004204006</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2442,43 +2430,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B37" t="n">
-        <v>243.32</v>
+        <v>53.91</v>
       </c>
       <c r="C37" t="n">
-        <v>7.812087172118972</v>
+        <v>3.687296561971278</v>
       </c>
       <c r="D37" t="n">
-        <v>7.79</v>
+        <v>3.69</v>
       </c>
       <c r="E37" t="n">
-        <v>70.1153640084721</v>
+        <v>30.39315961751112</v>
       </c>
       <c r="F37" t="n">
-        <v>70.02</v>
+        <v>30.39</v>
       </c>
       <c r="G37" t="n">
-        <v>9.258750060204248</v>
+        <v>3.531444910869012</v>
       </c>
       <c r="H37" t="n">
-        <v>491.8226682172628</v>
+        <v>146.5888239927882</v>
       </c>
       <c r="I37" t="n">
         <v>480</v>
       </c>
       <c r="J37" t="n">
-        <v>10.24630558785964</v>
+        <v>3.053933833183088</v>
       </c>
       <c r="K37" t="n">
         <v>25</v>
       </c>
       <c r="L37" t="n">
-        <v>7947.87</v>
+        <v>619.1799999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>3393.505225853706</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2500,25 +2488,25 @@
         <v>400</v>
       </c>
       <c r="B38" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5062059157706659</v>
+        <v>0.09999999999999948</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0.04455260831903524</v>
+        <v>0.4000000000000003</v>
       </c>
       <c r="H38" t="n">
-        <v>3.330467295850505</v>
+        <v>0.2466380007445908</v>
       </c>
       <c r="I38" t="n">
         <v>480</v>
@@ -2530,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>74.89</v>
+        <v>74.64</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2552,40 +2540,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B39" t="n">
-        <v>23.3</v>
+        <v>0.02</v>
       </c>
       <c r="C39" t="n">
-        <v>3.288398309513191</v>
+        <v>0.1004999999999996</v>
       </c>
       <c r="D39" t="n">
-        <v>3.29</v>
+        <v>0.1</v>
       </c>
       <c r="E39" t="n">
-        <v>25.73191239117592</v>
+        <v>0.5</v>
       </c>
       <c r="F39" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1.697039565022926</v>
+        <v>0.001738545336618067</v>
       </c>
       <c r="H39" t="n">
-        <v>66.27612124155526</v>
+        <v>0.2461340597551967</v>
       </c>
       <c r="I39" t="n">
         <v>480</v>
       </c>
       <c r="J39" t="n">
-        <v>1.380752525865735</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>347.63</v>
+        <v>73.89</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2607,43 +2595,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B40" t="n">
-        <v>54.21</v>
+        <v>0.02</v>
       </c>
       <c r="C40" t="n">
-        <v>5.061279034437455</v>
+        <v>0.1035070271243619</v>
       </c>
       <c r="D40" t="n">
-        <v>5.06</v>
+        <v>0.1</v>
       </c>
       <c r="E40" t="n">
-        <v>41.08026419296534</v>
+        <v>3.0070271243615</v>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
+        <v>3.01</v>
       </c>
       <c r="G40" t="n">
-        <v>2.736966335662</v>
+        <v>0.001830167891062257</v>
       </c>
       <c r="H40" t="n">
-        <v>130.0677048513072</v>
+        <v>0.2561056359691813</v>
       </c>
       <c r="I40" t="n">
         <v>480</v>
       </c>
       <c r="J40" t="n">
-        <v>2.709743851068899</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>10</v>
       </c>
       <c r="L40" t="n">
-        <v>1091.21</v>
+        <v>73.36</v>
       </c>
       <c r="M40" t="n">
-        <v>135.6151477382022</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2662,43 +2650,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B41" t="n">
-        <v>94.64</v>
+        <v>2.42</v>
       </c>
       <c r="C41" t="n">
-        <v>6.7309938155791</v>
+        <v>1.070436009185052</v>
       </c>
       <c r="D41" t="n">
-        <v>6.73</v>
+        <v>1.07</v>
       </c>
       <c r="E41" t="n">
-        <v>55.08553755831472</v>
+        <v>8.83187067912413</v>
       </c>
       <c r="F41" t="n">
-        <v>55</v>
+        <v>8.83</v>
       </c>
       <c r="G41" t="n">
-        <v>3.934330402927592</v>
+        <v>0.1927485396968685</v>
       </c>
       <c r="H41" t="n">
-        <v>202.8924452960736</v>
+        <v>10.71904032954932</v>
       </c>
       <c r="I41" t="n">
         <v>480</v>
       </c>
       <c r="J41" t="n">
-        <v>4.226925943668201</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>15</v>
       </c>
       <c r="L41" t="n">
-        <v>2457.73</v>
+        <v>12.62</v>
       </c>
       <c r="M41" t="n">
-        <v>839.2971895631372</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2717,43 +2705,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B42" t="n">
-        <v>136.27</v>
+        <v>10.69</v>
       </c>
       <c r="C42" t="n">
-        <v>8.119233418072971</v>
+        <v>2.279745489967828</v>
       </c>
       <c r="D42" t="n">
-        <v>8.109999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="E42" t="n">
-        <v>66.22798758325713</v>
+        <v>18.03810184138559</v>
       </c>
       <c r="F42" t="n">
-        <v>66.14</v>
+        <v>18.04</v>
       </c>
       <c r="G42" t="n">
-        <v>5.080664111661002</v>
+        <v>0.8516728279702823</v>
       </c>
       <c r="H42" t="n">
-        <v>271.2756597300116</v>
+        <v>35.13572880729871</v>
       </c>
       <c r="I42" t="n">
         <v>480</v>
       </c>
       <c r="J42" t="n">
-        <v>5.651576244375241</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>20</v>
       </c>
       <c r="L42" t="n">
-        <v>4202.45</v>
+        <v>56.88</v>
       </c>
       <c r="M42" t="n">
-        <v>1861.221955708581</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2772,46 +2760,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B43" t="n">
-        <v>175.26</v>
+        <v>30.28</v>
       </c>
       <c r="C43" t="n">
-        <v>9.256918528649962</v>
+        <v>3.884212139687461</v>
       </c>
       <c r="D43" t="n">
-        <v>9.24</v>
+        <v>3.88</v>
       </c>
       <c r="E43" t="n">
-        <v>75.21441008968623</v>
+        <v>32.48895467298318</v>
       </c>
       <c r="F43" t="n">
-        <v>75.12</v>
+        <v>32.49</v>
       </c>
       <c r="G43" t="n">
-        <v>6.105365099687184</v>
+        <v>1.894208440432259</v>
       </c>
       <c r="H43" t="n">
-        <v>331.2912047984769</v>
+        <v>80.66386723943839</v>
       </c>
       <c r="I43" t="n">
         <v>480</v>
       </c>
       <c r="J43" t="n">
-        <v>6.90190009996827</v>
+        <v>1.680497234154966</v>
       </c>
       <c r="K43" t="n">
         <v>25</v>
       </c>
       <c r="L43" t="n">
-        <v>6105.81</v>
+        <v>376.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3075.332975162576</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2843.625931711033</v>
+        <v>0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2830,25 +2818,25 @@
         <v>600</v>
       </c>
       <c r="B44" t="n">
-        <v>0.83</v>
+        <v>0.03</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5040400926720435</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D44" t="n">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06625827527107217</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H44" t="n">
-        <v>4.961439594440076</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I44" t="n">
         <v>480</v>
@@ -2860,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>112.33</v>
+        <v>111.96</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2882,40 +2870,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B45" t="n">
-        <v>34.66</v>
+        <v>0.03</v>
       </c>
       <c r="C45" t="n">
-        <v>3.287613472256953</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D45" t="n">
-        <v>3.29</v>
+        <v>0.1</v>
       </c>
       <c r="E45" t="n">
-        <v>25.72852642165479</v>
+        <v>0.5</v>
       </c>
       <c r="F45" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>2.525595930162866</v>
+        <v>0.00259903747292395</v>
       </c>
       <c r="H45" t="n">
-        <v>98.62134750433191</v>
+        <v>0.3679579883208992</v>
       </c>
       <c r="I45" t="n">
         <v>480</v>
       </c>
       <c r="J45" t="n">
-        <v>2.054611406340248</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>517.2</v>
+        <v>110.46</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2937,43 +2925,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B46" t="n">
-        <v>78.43000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="C46" t="n">
-        <v>4.98346704412087</v>
+        <v>0.1035070135211677</v>
       </c>
       <c r="D46" t="n">
-        <v>4.98</v>
+        <v>0.1</v>
       </c>
       <c r="E46" t="n">
-        <v>41.01095169733355</v>
+        <v>3.007013521167718</v>
       </c>
       <c r="F46" t="n">
-        <v>40.93</v>
+        <v>3.01</v>
       </c>
       <c r="G46" t="n">
-        <v>4.0058134148707</v>
+        <v>0.002714981170575139</v>
       </c>
       <c r="H46" t="n">
-        <v>189.328836781443</v>
+        <v>0.379922529963362</v>
       </c>
       <c r="I46" t="n">
         <v>480</v>
       </c>
       <c r="J46" t="n">
-        <v>3.944350766280063</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>10</v>
       </c>
       <c r="L46" t="n">
-        <v>1579.46</v>
+        <v>108.82</v>
       </c>
       <c r="M46" t="n">
-        <v>120.2653060945335</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -2992,43 +2980,43 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B47" t="n">
-        <v>129.18</v>
+        <v>3.57</v>
       </c>
       <c r="C47" t="n">
-        <v>6.480256974851422</v>
+        <v>1.07042836396181</v>
       </c>
       <c r="D47" t="n">
-        <v>6.48</v>
+        <v>1.07</v>
       </c>
       <c r="E47" t="n">
-        <v>54.8889848147075</v>
+        <v>8.831812621571924</v>
       </c>
       <c r="F47" t="n">
-        <v>54.8</v>
+        <v>8.83</v>
       </c>
       <c r="G47" t="n">
-        <v>5.498540148269834</v>
+        <v>0.2848852450528245</v>
       </c>
       <c r="H47" t="n">
-        <v>281.1153951627966</v>
+        <v>15.84294776398005</v>
       </c>
       <c r="I47" t="n">
         <v>480</v>
       </c>
       <c r="J47" t="n">
-        <v>5.856570732558263</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>15</v>
       </c>
       <c r="L47" t="n">
-        <v>3350.67</v>
+        <v>18.65</v>
       </c>
       <c r="M47" t="n">
-        <v>1072.605257070818</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3047,43 +3035,43 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B48" t="n">
-        <v>176.87</v>
+        <v>15.81</v>
       </c>
       <c r="C48" t="n">
-        <v>7.664714646733268</v>
+        <v>2.279034004975716</v>
       </c>
       <c r="D48" t="n">
-        <v>7.65</v>
+        <v>2.28</v>
       </c>
       <c r="E48" t="n">
-        <v>65.92292191239629</v>
+        <v>18.03266895933359</v>
       </c>
       <c r="F48" t="n">
-        <v>65.83</v>
+        <v>18.03</v>
       </c>
       <c r="G48" t="n">
-        <v>6.805841069862574</v>
+        <v>1.259779452021495</v>
       </c>
       <c r="H48" t="n">
-        <v>360.2094839645756</v>
+        <v>51.9785597125605</v>
       </c>
       <c r="I48" t="n">
         <v>480</v>
       </c>
       <c r="J48" t="n">
-        <v>7.504364249261992</v>
+        <v>1.082886660678344</v>
       </c>
       <c r="K48" t="n">
         <v>20</v>
       </c>
       <c r="L48" t="n">
-        <v>5441.16</v>
+        <v>84.09</v>
       </c>
       <c r="M48" t="n">
-        <v>2260.787958865605</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3102,46 +3090,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B49" t="n">
-        <v>219.38</v>
+        <v>44.92</v>
       </c>
       <c r="C49" t="n">
-        <v>8.606635552794639</v>
+        <v>3.880265029275787</v>
       </c>
       <c r="D49" t="n">
-        <v>8.58</v>
+        <v>3.88</v>
       </c>
       <c r="E49" t="n">
-        <v>74.90387291394637</v>
+        <v>32.45102022646769</v>
       </c>
       <c r="F49" t="n">
-        <v>74.81</v>
+        <v>32.45</v>
       </c>
       <c r="G49" t="n">
-        <v>7.924475710361778</v>
+        <v>2.812354043564242</v>
       </c>
       <c r="H49" t="n">
-        <v>426.7833398908897</v>
+        <v>119.7043290764857</v>
       </c>
       <c r="I49" t="n">
         <v>480</v>
       </c>
       <c r="J49" t="n">
-        <v>8.891319581060204</v>
+        <v>2.493840189093453</v>
       </c>
       <c r="K49" t="n">
         <v>25</v>
       </c>
       <c r="L49" t="n">
-        <v>7625.23</v>
+        <v>557.8200000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>3608.054814196842</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1987.332370487607</v>
+        <v>0</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3160,25 +3148,25 @@
         <v>800</v>
       </c>
       <c r="B50" t="n">
-        <v>1.13</v>
+        <v>0.04</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5092667921025946</v>
+        <v>0.09999999999999921</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09118171325285371</v>
+        <v>0.8000000000000006</v>
       </c>
       <c r="H50" t="n">
-        <v>6.725696822062408</v>
+        <v>0.4932760014891795</v>
       </c>
       <c r="I50" t="n">
         <v>480</v>
@@ -3190,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>149.78</v>
+        <v>149.27</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3212,40 +3200,40 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="B51" t="n">
-        <v>46.4</v>
+        <v>0.04</v>
       </c>
       <c r="C51" t="n">
-        <v>3.287946626279667</v>
+        <v>0.1004999999999993</v>
       </c>
       <c r="D51" t="n">
-        <v>3.29</v>
+        <v>0.1</v>
       </c>
       <c r="E51" t="n">
-        <v>25.72478272939507</v>
+        <v>0.5</v>
       </c>
       <c r="F51" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G51" t="n">
-        <v>3.380708433703578</v>
+        <v>0.003420017215215777</v>
       </c>
       <c r="H51" t="n">
-        <v>132.019769600008</v>
+        <v>0.4841879609830744</v>
       </c>
       <c r="I51" t="n">
         <v>480</v>
       </c>
       <c r="J51" t="n">
-        <v>2.750411866666833</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>5</v>
       </c>
       <c r="L51" t="n">
-        <v>692.4</v>
+        <v>145.36</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3267,43 +3255,43 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="B52" t="n">
-        <v>101.67</v>
+        <v>0.04</v>
       </c>
       <c r="C52" t="n">
-        <v>4.89799353667312</v>
+        <v>0.1035070005426104</v>
       </c>
       <c r="D52" t="n">
-        <v>4.9</v>
+        <v>0.1</v>
       </c>
       <c r="E52" t="n">
-        <v>40.93911469195518</v>
+        <v>3.007000542610385</v>
       </c>
       <c r="F52" t="n">
-        <v>40.86</v>
+        <v>3.01</v>
       </c>
       <c r="G52" t="n">
-        <v>5.261171088387377</v>
+        <v>0.00357185254822774</v>
       </c>
       <c r="H52" t="n">
-        <v>247.1156452915369</v>
+        <v>0.4998293685044642</v>
       </c>
       <c r="I52" t="n">
         <v>480</v>
       </c>
       <c r="J52" t="n">
-        <v>5.148242610240353</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>2049.34</v>
+        <v>143.17</v>
       </c>
       <c r="M52" t="n">
-        <v>93.08452682502073</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3322,43 +3310,43 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B53" t="n">
-        <v>161.64</v>
+        <v>4.73</v>
       </c>
       <c r="C53" t="n">
-        <v>6.24053326238892</v>
+        <v>1.070421008442392</v>
       </c>
       <c r="D53" t="n">
-        <v>6.23</v>
+        <v>1.07</v>
       </c>
       <c r="E53" t="n">
-        <v>54.69485951825559</v>
+        <v>8.831756764020099</v>
       </c>
       <c r="F53" t="n">
-        <v>54.61</v>
+        <v>8.83</v>
       </c>
       <c r="G53" t="n">
-        <v>7.048054203656798</v>
+        <v>0.3770195221973868</v>
       </c>
       <c r="H53" t="n">
-        <v>357.0388615391628</v>
+        <v>20.9667468307949</v>
       </c>
       <c r="I53" t="n">
         <v>480</v>
       </c>
       <c r="J53" t="n">
-        <v>7.438309615399224</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>15</v>
       </c>
       <c r="L53" t="n">
-        <v>4188.98</v>
+        <v>24.68</v>
       </c>
       <c r="M53" t="n">
-        <v>1249.265582174902</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3377,43 +3365,43 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B54" t="n">
-        <v>213.51</v>
+        <v>21.01</v>
       </c>
       <c r="C54" t="n">
-        <v>7.248824891525107</v>
+        <v>2.278322918379824</v>
       </c>
       <c r="D54" t="n">
-        <v>7.23</v>
+        <v>2.28</v>
       </c>
       <c r="E54" t="n">
-        <v>65.72276162828116</v>
+        <v>18.02723950670171</v>
       </c>
       <c r="F54" t="n">
-        <v>65.63</v>
+        <v>18.03</v>
       </c>
       <c r="G54" t="n">
-        <v>8.481099168900494</v>
+        <v>1.6741454004983</v>
       </c>
       <c r="H54" t="n">
-        <v>444.5143490971416</v>
+        <v>69.08383335516423</v>
       </c>
       <c r="I54" t="n">
         <v>480</v>
       </c>
       <c r="J54" t="n">
-        <v>9.26071560619045</v>
+        <v>1.439246528232588</v>
       </c>
       <c r="K54" t="n">
         <v>20</v>
       </c>
       <c r="L54" t="n">
-        <v>6563.63</v>
+        <v>111.7</v>
       </c>
       <c r="M54" t="n">
-        <v>2544.136756340772</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3432,46 +3420,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B55" t="n">
-        <v>255.62</v>
+        <v>59.67</v>
       </c>
       <c r="C55" t="n">
-        <v>8.034694771925412</v>
+        <v>3.876431436589105</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>3.88</v>
       </c>
       <c r="E55" t="n">
-        <v>74.69839944568575</v>
+        <v>32.41262245062409</v>
       </c>
       <c r="F55" t="n">
-        <v>74.59999999999999</v>
+        <v>32.41</v>
       </c>
       <c r="G55" t="n">
-        <v>9.573205787343412</v>
+        <v>3.738787598375051</v>
       </c>
       <c r="H55" t="n">
-        <v>510.9900934751601</v>
+        <v>159.0614403797387</v>
       </c>
       <c r="I55" t="n">
         <v>480</v>
       </c>
       <c r="J55" t="n">
-        <v>10.64562694739917</v>
+        <v>3.313780007911223</v>
       </c>
       <c r="K55" t="n">
         <v>25</v>
       </c>
       <c r="L55" t="n">
-        <v>8878.629999999999</v>
+        <v>739.91</v>
       </c>
       <c r="M55" t="n">
-        <v>3927.926131898766</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1419.129972170006</v>
+        <v>0</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3490,25 +3478,25 @@
         <v>400</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5079570765669413</v>
+        <v>0.09999999999999948</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G56" t="n">
-        <v>0.03591683497244551</v>
+        <v>0.4000000000000003</v>
       </c>
       <c r="H56" t="n">
-        <v>3.348978430895361</v>
+        <v>0.2466380007445908</v>
       </c>
       <c r="I56" t="n">
         <v>490</v>
@@ -3520,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>74.89</v>
+        <v>74.64</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -3545,25 +3533,25 @@
         <v>393</v>
       </c>
       <c r="B57" t="n">
-        <v>12.64</v>
+        <v>0.02</v>
       </c>
       <c r="C57" t="n">
-        <v>2.428356076867948</v>
+        <v>0.1004999999999996</v>
       </c>
       <c r="D57" t="n">
-        <v>2.43</v>
+        <v>0.1</v>
       </c>
       <c r="E57" t="n">
-        <v>22.63759945930896</v>
+        <v>0.5</v>
       </c>
       <c r="F57" t="n">
-        <v>22.57</v>
+        <v>0.5</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8064943440563968</v>
+        <v>0.001381365838781822</v>
       </c>
       <c r="H57" t="n">
-        <v>40.53394767234678</v>
+        <v>0.2442694077873543</v>
       </c>
       <c r="I57" t="n">
         <v>490</v>
@@ -3575,7 +3563,7 @@
         <v>5</v>
       </c>
       <c r="L57" t="n">
-        <v>204.08</v>
+        <v>73.33</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -3597,40 +3585,40 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B58" t="n">
-        <v>34.56</v>
+        <v>1.91</v>
       </c>
       <c r="C58" t="n">
-        <v>4.04654882356829</v>
+        <v>0.952567772232379</v>
       </c>
       <c r="D58" t="n">
-        <v>4.05</v>
+        <v>0.95</v>
       </c>
       <c r="E58" t="n">
-        <v>36.60658813878631</v>
+        <v>8.740271944587818</v>
       </c>
       <c r="F58" t="n">
-        <v>36.55</v>
+        <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>1.729564334495355</v>
+        <v>0.1215728325703252</v>
       </c>
       <c r="H58" t="n">
-        <v>90.59037230633631</v>
+        <v>8.842775993959764</v>
       </c>
       <c r="I58" t="n">
         <v>490</v>
       </c>
       <c r="J58" t="n">
-        <v>1.848783108292578</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>10</v>
       </c>
       <c r="L58" t="n">
-        <v>651.22</v>
+        <v>79.47</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -3652,43 +3640,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B59" t="n">
-        <v>65.5</v>
+        <v>7.81</v>
       </c>
       <c r="C59" t="n">
-        <v>5.607023702776904</v>
+        <v>1.946334049286281</v>
       </c>
       <c r="D59" t="n">
-        <v>5.61</v>
+        <v>1.95</v>
       </c>
       <c r="E59" t="n">
-        <v>50.17685495958609</v>
+        <v>18.05122938038485</v>
       </c>
       <c r="F59" t="n">
-        <v>50.12</v>
+        <v>18.05</v>
       </c>
       <c r="G59" t="n">
-        <v>2.636956467824409</v>
+        <v>0.4983226165256324</v>
       </c>
       <c r="H59" t="n">
-        <v>150.9311399154538</v>
+        <v>27.33289891387324</v>
       </c>
       <c r="I59" t="n">
         <v>490</v>
       </c>
       <c r="J59" t="n">
-        <v>3.080227345213342</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>15</v>
       </c>
       <c r="L59" t="n">
-        <v>1576.08</v>
+        <v>39.52</v>
       </c>
       <c r="M59" t="n">
-        <v>360.0537005946441</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -3707,43 +3695,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B60" t="n">
-        <v>99.3</v>
+        <v>19.37</v>
       </c>
       <c r="C60" t="n">
-        <v>6.967904727364588</v>
+        <v>3.089499659366174</v>
       </c>
       <c r="D60" t="n">
-        <v>6.97</v>
+        <v>3.09</v>
       </c>
       <c r="E60" t="n">
-        <v>63.60530106174878</v>
+        <v>29.22187253510036</v>
       </c>
       <c r="F60" t="n">
-        <v>63.54</v>
+        <v>29.22</v>
       </c>
       <c r="G60" t="n">
-        <v>3.545752116113752</v>
+        <v>1.204207182516201</v>
       </c>
       <c r="H60" t="n">
-        <v>209.9956531187839</v>
+        <v>56.46943250933603</v>
       </c>
       <c r="I60" t="n">
         <v>490</v>
       </c>
       <c r="J60" t="n">
-        <v>4.285625573852733</v>
+        <v>1.152437398149715</v>
       </c>
       <c r="K60" t="n">
         <v>20</v>
       </c>
       <c r="L60" t="n">
-        <v>2962.47</v>
+        <v>207.31</v>
       </c>
       <c r="M60" t="n">
-        <v>1080.445982677989</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -3762,43 +3750,43 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B61" t="n">
-        <v>131.82</v>
+        <v>43.9</v>
       </c>
       <c r="C61" t="n">
-        <v>8.11507745147131</v>
+        <v>4.689778490119448</v>
       </c>
       <c r="D61" t="n">
-        <v>8.109999999999999</v>
+        <v>4.69</v>
       </c>
       <c r="E61" t="n">
-        <v>75.69092922904487</v>
+        <v>41.66814677083841</v>
       </c>
       <c r="F61" t="n">
-        <v>75.63</v>
+        <v>41.67</v>
       </c>
       <c r="G61" t="n">
-        <v>4.373683388519304</v>
+        <v>1.979567935280509</v>
       </c>
       <c r="H61" t="n">
-        <v>262.470681107669</v>
+        <v>108.5626849522042</v>
       </c>
       <c r="I61" t="n">
         <v>490</v>
       </c>
       <c r="J61" t="n">
-        <v>5.356544512401408</v>
+        <v>2.215564999024575</v>
       </c>
       <c r="K61" t="n">
         <v>25</v>
       </c>
       <c r="L61" t="n">
-        <v>4638.22</v>
+        <v>713.28</v>
       </c>
       <c r="M61" t="n">
-        <v>2067.336880092389</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -3820,25 +3808,25 @@
         <v>600</v>
       </c>
       <c r="B62" t="n">
-        <v>0.85</v>
+        <v>0.03</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5105550807903367</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G62" t="n">
-        <v>0.05442776400487604</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H62" t="n">
-        <v>5.064768824583651</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I62" t="n">
         <v>490</v>
@@ -3850,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>112.34</v>
+        <v>111.96</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3872,40 +3860,40 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B63" t="n">
-        <v>18.97</v>
+        <v>0.03</v>
       </c>
       <c r="C63" t="n">
-        <v>2.4277550253622</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D63" t="n">
-        <v>2.43</v>
+        <v>0.1</v>
       </c>
       <c r="E63" t="n">
-        <v>22.63448889347154</v>
+        <v>0.5</v>
       </c>
       <c r="F63" t="n">
-        <v>22.56</v>
+        <v>0.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1.2101683012488</v>
+        <v>0.00206326144367668</v>
       </c>
       <c r="H63" t="n">
-        <v>60.82831899258679</v>
+        <v>0.3648502350411618</v>
       </c>
       <c r="I63" t="n">
         <v>490</v>
       </c>
       <c r="J63" t="n">
-        <v>1.241394265154832</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>5</v>
       </c>
       <c r="L63" t="n">
-        <v>306.23</v>
+        <v>109.53</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -3930,37 +3918,37 @@
         <v>579</v>
       </c>
       <c r="B64" t="n">
-        <v>51.4</v>
+        <v>2.87</v>
       </c>
       <c r="C64" t="n">
-        <v>4.034400531772845</v>
+        <v>0.9525631159963204</v>
       </c>
       <c r="D64" t="n">
-        <v>4.03</v>
+        <v>0.95</v>
       </c>
       <c r="E64" t="n">
-        <v>36.56853395712984</v>
+        <v>8.740228318619845</v>
       </c>
       <c r="F64" t="n">
-        <v>36.51</v>
+        <v>8.74</v>
       </c>
       <c r="G64" t="n">
-        <v>2.577857887330508</v>
+        <v>0.1828311218394274</v>
       </c>
       <c r="H64" t="n">
-        <v>134.8819632501449</v>
+        <v>13.29851203235945</v>
       </c>
       <c r="I64" t="n">
         <v>490</v>
       </c>
       <c r="J64" t="n">
-        <v>2.752693127553977</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>10</v>
       </c>
       <c r="L64" t="n">
-        <v>968.14</v>
+        <v>119.51</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -3982,43 +3970,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B65" t="n">
-        <v>92.95999999999999</v>
+        <v>11.77</v>
       </c>
       <c r="C65" t="n">
-        <v>5.463403107745207</v>
+        <v>1.945856268957374</v>
       </c>
       <c r="D65" t="n">
-        <v>5.46</v>
+        <v>1.95</v>
       </c>
       <c r="E65" t="n">
-        <v>50.05386790403427</v>
+        <v>18.04675288283299</v>
       </c>
       <c r="F65" t="n">
-        <v>49.99</v>
+        <v>18.05</v>
       </c>
       <c r="G65" t="n">
-        <v>3.801038356320761</v>
+        <v>0.751069989487262</v>
       </c>
       <c r="H65" t="n">
-        <v>216.4036676765207</v>
+        <v>41.20003851819646</v>
       </c>
       <c r="I65" t="n">
         <v>490</v>
       </c>
       <c r="J65" t="n">
-        <v>4.416401381153484</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
         <v>15</v>
       </c>
       <c r="L65" t="n">
-        <v>2236.69</v>
+        <v>59.54</v>
       </c>
       <c r="M65" t="n">
-        <v>473.0688796453624</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -4037,43 +4025,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B66" t="n">
-        <v>132.69</v>
+        <v>28.97</v>
       </c>
       <c r="C66" t="n">
-        <v>6.632737534381634</v>
+        <v>3.087812426699341</v>
       </c>
       <c r="D66" t="n">
-        <v>6.63</v>
+        <v>3.09</v>
       </c>
       <c r="E66" t="n">
-        <v>63.3447167512938</v>
+        <v>29.19695893702844</v>
       </c>
       <c r="F66" t="n">
-        <v>63.28</v>
+        <v>29.2</v>
       </c>
       <c r="G66" t="n">
-        <v>4.860219268552568</v>
+        <v>1.801961321029296</v>
       </c>
       <c r="H66" t="n">
-        <v>286.1159669589165</v>
+        <v>84.47824962816217</v>
       </c>
       <c r="I66" t="n">
         <v>490</v>
       </c>
       <c r="J66" t="n">
-        <v>5.8391013665085</v>
+        <v>1.72404591077882</v>
       </c>
       <c r="K66" t="n">
         <v>20</v>
       </c>
       <c r="L66" t="n">
-        <v>3952.07</v>
+        <v>309.72</v>
       </c>
       <c r="M66" t="n">
-        <v>1334.085797032848</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -4092,43 +4080,43 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B67" t="n">
-        <v>170.51</v>
+        <v>65.09</v>
       </c>
       <c r="C67" t="n">
-        <v>7.580765107720373</v>
+        <v>4.662200543303587</v>
       </c>
       <c r="D67" t="n">
-        <v>7.57</v>
+        <v>4.66</v>
       </c>
       <c r="E67" t="n">
-        <v>75.33397142951947</v>
+        <v>41.59858536527345</v>
       </c>
       <c r="F67" t="n">
-        <v>75.26000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.839038963021745</v>
+        <v>2.946229853907515</v>
       </c>
       <c r="H67" t="n">
-        <v>348.7693637420123</v>
+        <v>161.3098250719441</v>
       </c>
       <c r="I67" t="n">
         <v>490</v>
       </c>
       <c r="J67" t="n">
-        <v>7.117742117183925</v>
+        <v>3.292037246366205</v>
       </c>
       <c r="K67" t="n">
         <v>25</v>
       </c>
       <c r="L67" t="n">
-        <v>5984.27</v>
+        <v>1055.42</v>
       </c>
       <c r="M67" t="n">
-        <v>2471.46837697855</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -4150,25 +4138,25 @@
         <v>800</v>
       </c>
       <c r="B68" t="n">
-        <v>1.12</v>
+        <v>0.04</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5059813427392061</v>
+        <v>0.09999999999999921</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G68" t="n">
-        <v>0.07127595274300247</v>
+        <v>0.8000000000000006</v>
       </c>
       <c r="H68" t="n">
-        <v>6.656192365114959</v>
+        <v>0.4932760014891795</v>
       </c>
       <c r="I68" t="n">
         <v>490</v>
@@ -4180,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>149.78</v>
+        <v>149.27</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -4202,40 +4190,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="B69" t="n">
-        <v>25.07</v>
+        <v>0.04</v>
       </c>
       <c r="C69" t="n">
-        <v>2.427697581801716</v>
+        <v>0.1004999999999993</v>
       </c>
       <c r="D69" t="n">
-        <v>2.43</v>
+        <v>0.1</v>
       </c>
       <c r="E69" t="n">
-        <v>22.63165773355409</v>
+        <v>0.5</v>
       </c>
       <c r="F69" t="n">
-        <v>22.56</v>
+        <v>0.5</v>
       </c>
       <c r="G69" t="n">
-        <v>1.599807807521596</v>
+        <v>0.002769761529160528</v>
       </c>
       <c r="H69" t="n">
-        <v>80.41404577097376</v>
+        <v>0.4897819168866016</v>
       </c>
       <c r="I69" t="n">
         <v>490</v>
       </c>
       <c r="J69" t="n">
-        <v>1.641102974917832</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
         <v>5</v>
       </c>
       <c r="L69" t="n">
-        <v>404.83</v>
+        <v>147.03</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -4257,40 +4245,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="B70" t="n">
-        <v>67.38</v>
+        <v>3.85</v>
       </c>
       <c r="C70" t="n">
-        <v>4.023851535280781</v>
+        <v>0.9525582917517486</v>
       </c>
       <c r="D70" t="n">
-        <v>4.02</v>
+        <v>0.95</v>
       </c>
       <c r="E70" t="n">
-        <v>36.53193974398829</v>
+        <v>8.74018311851901</v>
       </c>
       <c r="F70" t="n">
-        <v>36.47</v>
+        <v>8.74</v>
       </c>
       <c r="G70" t="n">
-        <v>3.385892642275349</v>
+        <v>0.2456669637697428</v>
       </c>
       <c r="H70" t="n">
-        <v>177.0006516853051</v>
+        <v>17.86901254203484</v>
       </c>
       <c r="I70" t="n">
         <v>490</v>
       </c>
       <c r="J70" t="n">
-        <v>3.612258197659288</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>10</v>
       </c>
       <c r="L70" t="n">
-        <v>1268.83</v>
+        <v>160.58</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -4312,43 +4300,43 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="B71" t="n">
-        <v>116.37</v>
+        <v>15.63</v>
       </c>
       <c r="C71" t="n">
-        <v>5.340884184889665</v>
+        <v>1.945366136145783</v>
       </c>
       <c r="D71" t="n">
-        <v>5.34</v>
+        <v>1.95</v>
       </c>
       <c r="E71" t="n">
-        <v>49.93664897401337</v>
+        <v>18.04216065038175</v>
       </c>
       <c r="F71" t="n">
-        <v>49.88</v>
+        <v>18.04</v>
       </c>
       <c r="G71" t="n">
-        <v>4.824767853377601</v>
+        <v>0.9969712178633687</v>
       </c>
       <c r="H71" t="n">
-        <v>273.3510337021356</v>
+        <v>54.69442347870949</v>
       </c>
       <c r="I71" t="n">
         <v>490</v>
       </c>
       <c r="J71" t="n">
-        <v>5.578592524533379</v>
+        <v>1.116212724055296</v>
       </c>
       <c r="K71" t="n">
         <v>15</v>
       </c>
       <c r="L71" t="n">
-        <v>2800.18</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="M71" t="n">
-        <v>550.0806535983008</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -4370,40 +4358,40 @@
         <v>736</v>
       </c>
       <c r="B72" t="n">
-        <v>163.02</v>
+        <v>38.23</v>
       </c>
       <c r="C72" t="n">
-        <v>6.372548215035012</v>
+        <v>3.086132898786047</v>
       </c>
       <c r="D72" t="n">
-        <v>6.37</v>
+        <v>3.09</v>
       </c>
       <c r="E72" t="n">
-        <v>63.11001000572385</v>
+        <v>29.1724027726807</v>
       </c>
       <c r="F72" t="n">
-        <v>63.04</v>
+        <v>29.17</v>
       </c>
       <c r="G72" t="n">
-        <v>6.099909006949217</v>
+        <v>2.379584994436035</v>
       </c>
       <c r="H72" t="n">
-        <v>357.1086649040631</v>
+        <v>111.5291227621082</v>
       </c>
       <c r="I72" t="n">
         <v>490</v>
       </c>
       <c r="J72" t="n">
-        <v>7.287931936817613</v>
+        <v>2.276104546165474</v>
       </c>
       <c r="K72" t="n">
         <v>20</v>
       </c>
       <c r="L72" t="n">
-        <v>4848.53</v>
+        <v>408.36</v>
       </c>
       <c r="M72" t="n">
-        <v>1525.787469454112</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -4422,43 +4410,43 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B73" t="n">
-        <v>203.89</v>
+        <v>83.64</v>
       </c>
       <c r="C73" t="n">
-        <v>7.175760312857133</v>
+        <v>4.605562491225104</v>
       </c>
       <c r="D73" t="n">
-        <v>7.17</v>
+        <v>4.61</v>
       </c>
       <c r="E73" t="n">
-        <v>75.09401953636078</v>
+        <v>41.53092532880583</v>
       </c>
       <c r="F73" t="n">
-        <v>75.02</v>
+        <v>41.53</v>
       </c>
       <c r="G73" t="n">
-        <v>7.170596429487835</v>
+        <v>3.817843790310601</v>
       </c>
       <c r="H73" t="n">
-        <v>426.1913573006793</v>
+        <v>208.3085029742104</v>
       </c>
       <c r="I73" t="n">
         <v>490</v>
       </c>
       <c r="J73" t="n">
-        <v>8.697782802054679</v>
+        <v>4.251193938249191</v>
       </c>
       <c r="K73" t="n">
         <v>25</v>
       </c>
       <c r="L73" t="n">
-        <v>7147.65</v>
+        <v>1353.8</v>
       </c>
       <c r="M73" t="n">
-        <v>2752.928003364746</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -4480,25 +4468,25 @@
         <v>400</v>
       </c>
       <c r="B74" t="n">
-        <v>0.55</v>
+        <v>0.02</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5025798958994734</v>
+        <v>0.09999999999999948</v>
       </c>
       <c r="D74" t="n">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G74" t="n">
-        <v>0.03516043611297207</v>
+        <v>0.4000000000000003</v>
       </c>
       <c r="H74" t="n">
-        <v>3.292260535788664</v>
+        <v>0.2466380007445908</v>
       </c>
       <c r="I74" t="n">
         <v>490</v>
@@ -4510,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>74.88</v>
+        <v>74.64</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4532,28 +4520,28 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B75" t="n">
-        <v>14.45</v>
+        <v>0.02</v>
       </c>
       <c r="C75" t="n">
-        <v>2.593322895340278</v>
+        <v>0.1004999999999996</v>
       </c>
       <c r="D75" t="n">
-        <v>2.59</v>
+        <v>0.1</v>
       </c>
       <c r="E75" t="n">
-        <v>24.18708625098965</v>
+        <v>0.5</v>
       </c>
       <c r="F75" t="n">
-        <v>24.11</v>
+        <v>0.5</v>
       </c>
       <c r="G75" t="n">
-        <v>0.922132753537279</v>
+        <v>0.001374335987184968</v>
       </c>
       <c r="H75" t="n">
-        <v>45.15814103650796</v>
+        <v>0.2430263064754594</v>
       </c>
       <c r="I75" t="n">
         <v>490</v>
@@ -4565,7 +4553,7 @@
         <v>5</v>
       </c>
       <c r="L75" t="n">
-        <v>233.25</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -4587,40 +4575,40 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B76" t="n">
-        <v>37.24</v>
+        <v>2.14</v>
       </c>
       <c r="C76" t="n">
-        <v>4.227670281018405</v>
+        <v>1.011915128317295</v>
       </c>
       <c r="D76" t="n">
-        <v>4.23</v>
+        <v>1.01</v>
       </c>
       <c r="E76" t="n">
-        <v>38.9020431170023</v>
+        <v>9.296318893646946</v>
       </c>
       <c r="F76" t="n">
-        <v>38.84</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>1.804808479970713</v>
+        <v>0.1368369670601872</v>
       </c>
       <c r="H76" t="n">
-        <v>95.9302647168151</v>
+        <v>9.718237016529947</v>
       </c>
       <c r="I76" t="n">
         <v>490</v>
       </c>
       <c r="J76" t="n">
-        <v>1.957760504424798</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>734.1900000000001</v>
+        <v>11.59</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -4642,43 +4630,43 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B77" t="n">
-        <v>68.84999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>5.802041898473547</v>
+        <v>2.075745118144011</v>
       </c>
       <c r="D77" t="n">
-        <v>5.8</v>
+        <v>2.08</v>
       </c>
       <c r="E77" t="n">
-        <v>53.42744886301264</v>
+        <v>19.26423605865026</v>
       </c>
       <c r="F77" t="n">
-        <v>53.36</v>
+        <v>19.26</v>
       </c>
       <c r="G77" t="n">
-        <v>2.716588648302501</v>
+        <v>0.565292779708676</v>
       </c>
       <c r="H77" t="n">
-        <v>156.5231390714521</v>
+        <v>30.22773878993587</v>
       </c>
       <c r="I77" t="n">
         <v>490</v>
       </c>
       <c r="J77" t="n">
-        <v>3.19434977696841</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
         <v>15</v>
       </c>
       <c r="L77" t="n">
-        <v>1754.1</v>
+        <v>50</v>
       </c>
       <c r="M77" t="n">
-        <v>442.6543079725708</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -4697,43 +4685,43 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B78" t="n">
-        <v>103.1</v>
+        <v>22.66</v>
       </c>
       <c r="C78" t="n">
-        <v>7.167024889025558</v>
+        <v>3.337204825462822</v>
       </c>
       <c r="D78" t="n">
-        <v>7.17</v>
+        <v>3.34</v>
       </c>
       <c r="E78" t="n">
-        <v>67.79739016362232</v>
+        <v>31.71639134373398</v>
       </c>
       <c r="F78" t="n">
-        <v>67.73</v>
+        <v>31.72</v>
       </c>
       <c r="G78" t="n">
-        <v>3.629378207971285</v>
+        <v>1.319295914680757</v>
       </c>
       <c r="H78" t="n">
-        <v>215.608944480403</v>
+        <v>64.08233481837399</v>
       </c>
       <c r="I78" t="n">
         <v>490</v>
       </c>
       <c r="J78" t="n">
-        <v>4.400182540416388</v>
+        <v>1.307802751395388</v>
       </c>
       <c r="K78" t="n">
         <v>20</v>
       </c>
       <c r="L78" t="n">
-        <v>3269.47</v>
+        <v>269.26</v>
       </c>
       <c r="M78" t="n">
-        <v>1247.042582984951</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
@@ -4752,43 +4740,43 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>136.04</v>
+        <v>50.02</v>
       </c>
       <c r="C79" t="n">
-        <v>8.312272241561796</v>
+        <v>5.012598142384241</v>
       </c>
       <c r="D79" t="n">
-        <v>8.31</v>
+        <v>5.01</v>
       </c>
       <c r="E79" t="n">
-        <v>80.73514425991785</v>
+        <v>45.04299534490563</v>
       </c>
       <c r="F79" t="n">
-        <v>80.66</v>
+        <v>45.04</v>
       </c>
       <c r="G79" t="n">
-        <v>4.465369047888629</v>
+        <v>2.158574095881737</v>
       </c>
       <c r="H79" t="n">
-        <v>268.3226995235163</v>
+        <v>120.4741306327622</v>
       </c>
       <c r="I79" t="n">
         <v>490</v>
       </c>
       <c r="J79" t="n">
-        <v>5.475973459663599</v>
+        <v>2.458655727199228</v>
       </c>
       <c r="K79" t="n">
         <v>25</v>
       </c>
       <c r="L79" t="n">
-        <v>5097.53</v>
+        <v>881.85</v>
       </c>
       <c r="M79" t="n">
-        <v>2335.584417885399</v>
+        <v>295.7897666743277</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -4810,25 +4798,25 @@
         <v>600</v>
       </c>
       <c r="B80" t="n">
-        <v>0.85</v>
+        <v>0.03</v>
       </c>
       <c r="C80" t="n">
-        <v>0.5101561903210348</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G80" t="n">
-        <v>0.05434274972929903</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H80" t="n">
-        <v>5.058419272970567</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I80" t="n">
         <v>490</v>
@@ -4840,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>112.34</v>
+        <v>111.96</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -4862,40 +4850,40 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B81" t="n">
-        <v>21.56</v>
+        <v>0.03</v>
       </c>
       <c r="C81" t="n">
-        <v>2.592677157307687</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D81" t="n">
-        <v>2.59</v>
+        <v>0.1</v>
       </c>
       <c r="E81" t="n">
-        <v>24.18363205704567</v>
+        <v>0.5</v>
       </c>
       <c r="F81" t="n">
-        <v>24.11</v>
+        <v>0.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.375492563025987</v>
+        <v>0.002049201740482972</v>
       </c>
       <c r="H81" t="n">
-        <v>67.3664364212124</v>
+        <v>0.362364032417372</v>
       </c>
       <c r="I81" t="n">
         <v>490</v>
       </c>
       <c r="J81" t="n">
-        <v>1.374825233085967</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>5</v>
       </c>
       <c r="L81" t="n">
-        <v>347.93</v>
+        <v>108.78</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -4917,40 +4905,40 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B82" t="n">
-        <v>55.9</v>
+        <v>3.19</v>
       </c>
       <c r="C82" t="n">
-        <v>4.214618486065059</v>
+        <v>1.011910209124022</v>
       </c>
       <c r="D82" t="n">
-        <v>4.21</v>
+        <v>1.01</v>
       </c>
       <c r="E82" t="n">
-        <v>38.85842532318694</v>
+        <v>9.296272803937292</v>
       </c>
       <c r="F82" t="n">
-        <v>38.79</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>2.715334398027836</v>
+        <v>0.2038280837753391</v>
       </c>
       <c r="H82" t="n">
-        <v>144.1825933882806</v>
+        <v>14.47601094174142</v>
       </c>
       <c r="I82" t="n">
         <v>490</v>
       </c>
       <c r="J82" t="n">
-        <v>2.942501905883277</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>10</v>
       </c>
       <c r="L82" t="n">
-        <v>1101.65</v>
+        <v>17.27</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -4975,40 +4963,40 @@
         <v>568</v>
       </c>
       <c r="B83" t="n">
-        <v>98.78</v>
+        <v>13.34</v>
       </c>
       <c r="C83" t="n">
-        <v>5.646597925660334</v>
+        <v>2.075186311321927</v>
       </c>
       <c r="D83" t="n">
-        <v>5.65</v>
+        <v>2.08</v>
       </c>
       <c r="E83" t="n">
-        <v>53.28311545573602</v>
+        <v>19.25899936991762</v>
       </c>
       <c r="F83" t="n">
-        <v>53.21</v>
+        <v>19.26</v>
       </c>
       <c r="G83" t="n">
-        <v>3.959710320784424</v>
+        <v>0.8512292951146802</v>
       </c>
       <c r="H83" t="n">
-        <v>226.968847731093</v>
+        <v>45.52238123733824</v>
       </c>
       <c r="I83" t="n">
         <v>490</v>
       </c>
       <c r="J83" t="n">
-        <v>4.632017300634551</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
         <v>15</v>
       </c>
       <c r="L83" t="n">
-        <v>2515.45</v>
+        <v>75.25</v>
       </c>
       <c r="M83" t="n">
-        <v>591.279640617528</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -5027,43 +5015,43 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B84" t="n">
-        <v>141.94</v>
+        <v>33.91</v>
       </c>
       <c r="C84" t="n">
-        <v>6.811029280298139</v>
+        <v>3.334968661374559</v>
       </c>
       <c r="D84" t="n">
-        <v>6.81</v>
+        <v>3.33</v>
       </c>
       <c r="E84" t="n">
-        <v>67.49251496975123</v>
+        <v>31.68599004523123</v>
       </c>
       <c r="F84" t="n">
-        <v>67.42</v>
+        <v>31.69</v>
       </c>
       <c r="G84" t="n">
-        <v>5.127389473636017</v>
+        <v>1.975628910018692</v>
       </c>
       <c r="H84" t="n">
-        <v>302.879110145143</v>
+        <v>95.9343369376156</v>
       </c>
       <c r="I84" t="n">
         <v>490</v>
       </c>
       <c r="J84" t="n">
-        <v>6.181206329492715</v>
+        <v>1.957843610971747</v>
       </c>
       <c r="K84" t="n">
         <v>20</v>
       </c>
       <c r="L84" t="n">
-        <v>4491.57</v>
+        <v>402.51</v>
       </c>
       <c r="M84" t="n">
-        <v>1590.480000181502</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -5082,43 +5070,43 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="B85" t="n">
-        <v>180.9</v>
+        <v>72.39</v>
       </c>
       <c r="C85" t="n">
-        <v>7.737454835592246</v>
+        <v>4.953096339142779</v>
       </c>
       <c r="D85" t="n">
-        <v>7.73</v>
+        <v>4.95</v>
       </c>
       <c r="E85" t="n">
-        <v>80.34397557978269</v>
+        <v>44.95668940874183</v>
       </c>
       <c r="F85" t="n">
-        <v>80.27</v>
+        <v>44.96</v>
       </c>
       <c r="G85" t="n">
-        <v>6.134622957065542</v>
+        <v>3.148121881507747</v>
       </c>
       <c r="H85" t="n">
-        <v>367.0369256920854</v>
+        <v>175.1759531973228</v>
       </c>
       <c r="I85" t="n">
         <v>490</v>
       </c>
       <c r="J85" t="n">
-        <v>7.49054950392011</v>
+        <v>3.575019453006587</v>
       </c>
       <c r="K85" t="n">
         <v>25</v>
       </c>
       <c r="L85" t="n">
-        <v>6759.53</v>
+        <v>1273.46</v>
       </c>
       <c r="M85" t="n">
-        <v>2869.955569228096</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -5140,25 +5128,25 @@
         <v>800</v>
       </c>
       <c r="B86" t="n">
-        <v>1.15</v>
+        <v>0.04</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5125987709981427</v>
+        <v>0.09999999999999921</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>0.07315249547933443</v>
+        <v>0.8000000000000006</v>
       </c>
       <c r="H86" t="n">
-        <v>6.796463231596679</v>
+        <v>0.4932760014891795</v>
       </c>
       <c r="I86" t="n">
         <v>490</v>
@@ -5170,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>149.79</v>
+        <v>149.27</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -5192,40 +5180,40 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B87" t="n">
-        <v>28.81</v>
+        <v>0.04</v>
       </c>
       <c r="C87" t="n">
-        <v>2.59258351239537</v>
+        <v>0.1004999999999993</v>
       </c>
       <c r="D87" t="n">
-        <v>2.59</v>
+        <v>0.1</v>
       </c>
       <c r="E87" t="n">
-        <v>24.18024495207195</v>
+        <v>0.5</v>
       </c>
       <c r="F87" t="n">
-        <v>24.11</v>
+        <v>0.5</v>
       </c>
       <c r="G87" t="n">
-        <v>1.838535810812997</v>
+        <v>0.002752186900168393</v>
       </c>
       <c r="H87" t="n">
-        <v>90.04583247470046</v>
+        <v>0.4866741636068642</v>
       </c>
       <c r="I87" t="n">
         <v>490</v>
       </c>
       <c r="J87" t="n">
-        <v>1.837670050504091</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
         <v>5</v>
       </c>
       <c r="L87" t="n">
-        <v>465.05</v>
+        <v>146.1</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -5250,37 +5238,37 @@
         <v>767</v>
       </c>
       <c r="B88" t="n">
-        <v>73.19</v>
+        <v>4.28</v>
       </c>
       <c r="C88" t="n">
-        <v>4.182895082905866</v>
+        <v>1.011905084964359</v>
       </c>
       <c r="D88" t="n">
-        <v>4.18</v>
+        <v>1.01</v>
       </c>
       <c r="E88" t="n">
-        <v>38.8139899333966</v>
+        <v>9.296224793823066</v>
       </c>
       <c r="F88" t="n">
-        <v>38.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>3.574795254431875</v>
+        <v>0.2733121624733165</v>
       </c>
       <c r="H88" t="n">
-        <v>189.3502589168802</v>
+        <v>19.41085690956016</v>
       </c>
       <c r="I88" t="n">
         <v>490</v>
       </c>
       <c r="J88" t="n">
-        <v>3.864290998303678</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>10</v>
       </c>
       <c r="L88" t="n">
-        <v>1443.16</v>
+        <v>23.15</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -5302,43 +5290,43 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B89" t="n">
-        <v>123.81</v>
+        <v>17.79</v>
       </c>
       <c r="C89" t="n">
-        <v>5.490516890776978</v>
+        <v>2.074606687278343</v>
       </c>
       <c r="D89" t="n">
-        <v>5.49</v>
+        <v>2.07</v>
       </c>
       <c r="E89" t="n">
-        <v>53.14527575025819</v>
+        <v>19.25356759833656</v>
       </c>
       <c r="F89" t="n">
-        <v>53.08</v>
+        <v>19.25</v>
       </c>
       <c r="G89" t="n">
-        <v>5.047015426232663</v>
+        <v>1.135336997021862</v>
       </c>
       <c r="H89" t="n">
-        <v>287.6565142276439</v>
+        <v>60.72270672130526</v>
       </c>
       <c r="I89" t="n">
         <v>490</v>
       </c>
       <c r="J89" t="n">
-        <v>5.87054110668661</v>
+        <v>1.239238912679699</v>
       </c>
       <c r="K89" t="n">
         <v>15</v>
       </c>
       <c r="L89" t="n">
-        <v>3152.83</v>
+        <v>100.32</v>
       </c>
       <c r="M89" t="n">
-        <v>683.6439271021072</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -5357,43 +5345,43 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="B90" t="n">
-        <v>169.85</v>
+        <v>44.95</v>
       </c>
       <c r="C90" t="n">
-        <v>6.504741271265924</v>
+        <v>3.332705036244021</v>
       </c>
       <c r="D90" t="n">
-        <v>6.5</v>
+        <v>3.33</v>
       </c>
       <c r="E90" t="n">
-        <v>67.23977991613815</v>
+        <v>31.65547049653195</v>
       </c>
       <c r="F90" t="n">
-        <v>67.17</v>
+        <v>31.66</v>
       </c>
       <c r="G90" t="n">
-        <v>6.285359703936007</v>
+        <v>2.620314019884913</v>
       </c>
       <c r="H90" t="n">
-        <v>369.0727728225139</v>
+        <v>127.2016937283265</v>
       </c>
       <c r="I90" t="n">
         <v>490</v>
       </c>
       <c r="J90" t="n">
-        <v>7.5320974045411</v>
+        <v>2.595952933231152</v>
       </c>
       <c r="K90" t="n">
         <v>20</v>
       </c>
       <c r="L90" t="n">
-        <v>5367.05</v>
+        <v>532.92</v>
       </c>
       <c r="M90" t="n">
-        <v>1762.294955565692</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -5412,43 +5400,43 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B91" t="n">
-        <v>209.15</v>
+        <v>94.28</v>
       </c>
       <c r="C91" t="n">
-        <v>7.297991239232475</v>
+        <v>4.883011393406656</v>
       </c>
       <c r="D91" t="n">
-        <v>7.29</v>
+        <v>4.88</v>
       </c>
       <c r="E91" t="n">
-        <v>80.0859883007886</v>
+        <v>44.87131793582046</v>
       </c>
       <c r="F91" t="n">
-        <v>80.01000000000001</v>
+        <v>44.87</v>
       </c>
       <c r="G91" t="n">
-        <v>7.294076911529261</v>
+        <v>4.138571707267809</v>
       </c>
       <c r="H91" t="n">
-        <v>434.2840241466373</v>
+        <v>229.4467050576856</v>
       </c>
       <c r="I91" t="n">
         <v>490</v>
       </c>
       <c r="J91" t="n">
-        <v>8.862939268298719</v>
+        <v>4.682585817503789</v>
       </c>
       <c r="K91" t="n">
         <v>25</v>
       </c>
       <c r="L91" t="n">
-        <v>7805.43</v>
+        <v>1655.02</v>
       </c>
       <c r="M91" t="n">
-        <v>3086.75480250022</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5470,25 +5458,25 @@
         <v>400</v>
       </c>
       <c r="B92" t="n">
-        <v>0.57</v>
+        <v>0.02</v>
       </c>
       <c r="C92" t="n">
-        <v>0.510773391261352</v>
+        <v>0.09999999999999948</v>
       </c>
       <c r="D92" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G92" t="n">
-        <v>0.03631621331045794</v>
+        <v>0.4000000000000003</v>
       </c>
       <c r="H92" t="n">
-        <v>3.378830112661039</v>
+        <v>0.2466380007445908</v>
       </c>
       <c r="I92" t="n">
         <v>490</v>
@@ -5500,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>74.89</v>
+        <v>74.64</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -5522,40 +5510,40 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.35</v>
+        <v>0.02</v>
       </c>
       <c r="C93" t="n">
-        <v>2.758132243121028</v>
+        <v>0.1004999999999996</v>
       </c>
       <c r="D93" t="n">
-        <v>2.76</v>
+        <v>0.1</v>
       </c>
       <c r="E93" t="n">
-        <v>25.73188708911193</v>
+        <v>0.5</v>
       </c>
       <c r="F93" t="n">
-        <v>25.66</v>
+        <v>0.5</v>
       </c>
       <c r="G93" t="n">
-        <v>1.0430627358603</v>
+        <v>0.001367306135588114</v>
       </c>
       <c r="H93" t="n">
-        <v>49.85209726834766</v>
+        <v>0.2417832051635645</v>
       </c>
       <c r="I93" t="n">
         <v>490</v>
       </c>
       <c r="J93" t="n">
-        <v>1.01738974017036</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
         <v>5</v>
       </c>
       <c r="L93" t="n">
-        <v>265.77</v>
+        <v>72.58</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -5577,40 +5565,40 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B94" t="n">
-        <v>40.9</v>
+        <v>2.42</v>
       </c>
       <c r="C94" t="n">
-        <v>4.396307673329835</v>
+        <v>1.071098246728074</v>
       </c>
       <c r="D94" t="n">
-        <v>4.4</v>
+        <v>1.07</v>
       </c>
       <c r="E94" t="n">
-        <v>41.22948161394471</v>
+        <v>9.850827040244736</v>
       </c>
       <c r="F94" t="n">
-        <v>41.16</v>
+        <v>9.85</v>
       </c>
       <c r="G94" t="n">
-        <v>1.92791930813931</v>
+        <v>0.1541096944246965</v>
       </c>
       <c r="H94" t="n">
-        <v>103.7499967770645</v>
+        <v>10.70196052426422</v>
       </c>
       <c r="I94" t="n">
         <v>490</v>
       </c>
       <c r="J94" t="n">
-        <v>2.117346873001317</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>10</v>
       </c>
       <c r="L94" t="n">
-        <v>844.09</v>
+        <v>14.03</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -5632,43 +5620,43 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B95" t="n">
-        <v>74.54000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="C95" t="n">
-        <v>5.981246318930325</v>
+        <v>2.204796860165493</v>
       </c>
       <c r="D95" t="n">
-        <v>5.98</v>
+        <v>2.2</v>
       </c>
       <c r="E95" t="n">
-        <v>56.70245897433547</v>
+        <v>20.49261380269776</v>
       </c>
       <c r="F95" t="n">
-        <v>56.63</v>
+        <v>20.49</v>
       </c>
       <c r="G95" t="n">
-        <v>2.889816659999886</v>
+        <v>0.6411511288830889</v>
       </c>
       <c r="H95" t="n">
-        <v>167.4225768107987</v>
+        <v>33.47694229364599</v>
       </c>
       <c r="I95" t="n">
         <v>490</v>
       </c>
       <c r="J95" t="n">
-        <v>3.416787281853034</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>15</v>
       </c>
       <c r="L95" t="n">
-        <v>2006.21</v>
+        <v>62.97</v>
       </c>
       <c r="M95" t="n">
-        <v>548.1132837142566</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -5687,43 +5675,43 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B96" t="n">
-        <v>109.98</v>
+        <v>26.22</v>
       </c>
       <c r="C96" t="n">
-        <v>7.342575065397292</v>
+        <v>3.589846710236656</v>
       </c>
       <c r="D96" t="n">
-        <v>7.34</v>
+        <v>3.59</v>
       </c>
       <c r="E96" t="n">
-        <v>71.9981971927115</v>
+        <v>34.27791229238001</v>
       </c>
       <c r="F96" t="n">
-        <v>71.92</v>
+        <v>34.28</v>
       </c>
       <c r="G96" t="n">
-        <v>3.825345307872965</v>
+        <v>1.438479570290145</v>
       </c>
       <c r="H96" t="n">
-        <v>227.8023901135344</v>
+        <v>72.0453006516265</v>
       </c>
       <c r="I96" t="n">
         <v>490</v>
       </c>
       <c r="J96" t="n">
-        <v>4.649028369663968</v>
+        <v>1.470312258196459</v>
       </c>
       <c r="K96" t="n">
         <v>20</v>
       </c>
       <c r="L96" t="n">
-        <v>3695.63</v>
+        <v>342.21</v>
       </c>
       <c r="M96" t="n">
-        <v>1461.758937244834</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -5745,40 +5733,40 @@
         <v>367</v>
       </c>
       <c r="B97" t="n">
-        <v>143.87</v>
+        <v>56.35</v>
       </c>
       <c r="C97" t="n">
-        <v>8.477949891969866</v>
+        <v>5.305621048553126</v>
       </c>
       <c r="D97" t="n">
-        <v>8.470000000000001</v>
+        <v>5.31</v>
       </c>
       <c r="E97" t="n">
-        <v>85.77007583314244</v>
+        <v>48.48179629731079</v>
       </c>
       <c r="F97" t="n">
-        <v>85.69</v>
+        <v>48.48</v>
       </c>
       <c r="G97" t="n">
-        <v>4.68114098369625</v>
+        <v>2.345879639722098</v>
       </c>
       <c r="H97" t="n">
-        <v>281.561241247916</v>
+        <v>132.6990181059689</v>
       </c>
       <c r="I97" t="n">
         <v>490</v>
       </c>
       <c r="J97" t="n">
-        <v>5.746147780569713</v>
+        <v>2.708143226652427</v>
       </c>
       <c r="K97" t="n">
         <v>25</v>
       </c>
       <c r="L97" t="n">
-        <v>5719.92</v>
+        <v>1070.63</v>
       </c>
       <c r="M97" t="n">
-        <v>2678.983440771491</v>
+        <v>494.9307932845199</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -5800,25 +5788,25 @@
         <v>600</v>
       </c>
       <c r="B98" t="n">
-        <v>0.86</v>
+        <v>0.03</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5123846541644739</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G98" t="n">
-        <v>0.05481854655995434</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H98" t="n">
-        <v>5.093930481428742</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I98" t="n">
         <v>490</v>
@@ -5830,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>112.34</v>
+        <v>111.96</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -5852,40 +5840,40 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B99" t="n">
-        <v>24.34</v>
+        <v>0.03</v>
       </c>
       <c r="C99" t="n">
-        <v>2.75743257969444</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D99" t="n">
-        <v>2.76</v>
+        <v>0.1</v>
       </c>
       <c r="E99" t="n">
-        <v>25.72833333638504</v>
+        <v>0.5</v>
       </c>
       <c r="F99" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.553216316641843</v>
+        <v>0.002080836072668816</v>
       </c>
       <c r="H99" t="n">
-        <v>74.24179607218132</v>
+        <v>0.3679579883208992</v>
       </c>
       <c r="I99" t="n">
         <v>490</v>
       </c>
       <c r="J99" t="n">
-        <v>1.515138695350639</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
         <v>5</v>
       </c>
       <c r="L99" t="n">
-        <v>395.74</v>
+        <v>110.46</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -5907,40 +5895,40 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="B100" t="n">
-        <v>59.63</v>
+        <v>3.65</v>
       </c>
       <c r="C100" t="n">
-        <v>4.379594091300439</v>
+        <v>1.071092717840865</v>
       </c>
       <c r="D100" t="n">
-        <v>4.38</v>
+        <v>1.07</v>
       </c>
       <c r="E100" t="n">
-        <v>41.17924910603568</v>
+        <v>9.850775238091012</v>
       </c>
       <c r="F100" t="n">
-        <v>41.11</v>
+        <v>9.85</v>
       </c>
       <c r="G100" t="n">
-        <v>2.818274952749984</v>
+        <v>0.2331583741095331</v>
       </c>
       <c r="H100" t="n">
-        <v>151.487292236957</v>
+        <v>16.1914330739295</v>
       </c>
       <c r="I100" t="n">
         <v>490</v>
       </c>
       <c r="J100" t="n">
-        <v>3.091577392590959</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
         <v>10</v>
       </c>
       <c r="L100" t="n">
-        <v>1229.97</v>
+        <v>21.22</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -5962,43 +5950,43 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B101" t="n">
-        <v>103.77</v>
+        <v>15.08</v>
       </c>
       <c r="C101" t="n">
-        <v>5.818297228837779</v>
+        <v>2.204097180486317</v>
       </c>
       <c r="D101" t="n">
-        <v>5.82</v>
+        <v>2.2</v>
       </c>
       <c r="E101" t="n">
-        <v>56.54453434977582</v>
+        <v>20.48602854172669</v>
       </c>
       <c r="F101" t="n">
-        <v>56.47</v>
+        <v>20.49</v>
       </c>
       <c r="G101" t="n">
-        <v>4.087245818101216</v>
+        <v>0.9619617022943522</v>
       </c>
       <c r="H101" t="n">
-        <v>235.6317130948852</v>
+        <v>50.23398163782684</v>
       </c>
       <c r="I101" t="n">
         <v>490</v>
       </c>
       <c r="J101" t="n">
-        <v>4.808810471324188</v>
+        <v>1.02518329873116</v>
       </c>
       <c r="K101" t="n">
         <v>15</v>
       </c>
       <c r="L101" t="n">
-        <v>2790.97</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="M101" t="n">
-        <v>714.5458131975437</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
         <v>0</v>
@@ -6017,43 +6005,43 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B102" t="n">
-        <v>146.93</v>
+        <v>39.17</v>
       </c>
       <c r="C102" t="n">
-        <v>6.979685586509193</v>
+        <v>3.587471613356033</v>
       </c>
       <c r="D102" t="n">
-        <v>6.98</v>
+        <v>3.59</v>
       </c>
       <c r="E102" t="n">
-        <v>71.67309033102595</v>
+        <v>34.24064975891754</v>
       </c>
       <c r="F102" t="n">
-        <v>71.59999999999999</v>
+        <v>34.24</v>
       </c>
       <c r="G102" t="n">
-        <v>5.24135214425227</v>
+        <v>2.150222519095795</v>
       </c>
       <c r="H102" t="n">
-        <v>310.5143574181009</v>
+        <v>107.6637986107587</v>
       </c>
       <c r="I102" t="n">
         <v>490</v>
       </c>
       <c r="J102" t="n">
-        <v>6.337027702410223</v>
+        <v>2.197220379811403</v>
       </c>
       <c r="K102" t="n">
         <v>20</v>
       </c>
       <c r="L102" t="n">
-        <v>4925.59</v>
+        <v>510.6</v>
       </c>
       <c r="M102" t="n">
-        <v>1817.413597020087</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -6072,43 +6060,43 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B103" t="n">
-        <v>184.12</v>
+        <v>80.69</v>
       </c>
       <c r="C103" t="n">
-        <v>7.899225670966185</v>
+        <v>5.219680788863889</v>
       </c>
       <c r="D103" t="n">
-        <v>7.89</v>
+        <v>5.22</v>
       </c>
       <c r="E103" t="n">
-        <v>85.38779288468548</v>
+        <v>48.37607614836483</v>
       </c>
       <c r="F103" t="n">
-        <v>85.3</v>
+        <v>48.38</v>
       </c>
       <c r="G103" t="n">
-        <v>6.18357571000915</v>
+        <v>3.393686492547744</v>
       </c>
       <c r="H103" t="n">
-        <v>370.5274791083692</v>
+        <v>191.2574496691676</v>
       </c>
       <c r="I103" t="n">
         <v>490</v>
       </c>
       <c r="J103" t="n">
-        <v>7.561785287925902</v>
+        <v>3.903213258554441</v>
       </c>
       <c r="K103" t="n">
         <v>25</v>
       </c>
       <c r="L103" t="n">
-        <v>7300.71</v>
+        <v>1529.37</v>
       </c>
       <c r="M103" t="n">
-        <v>3182.215424446185</v>
+        <v>644.7840224204259</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
@@ -6130,25 +6118,25 @@
         <v>800</v>
       </c>
       <c r="B104" t="n">
-        <v>1.13</v>
+        <v>0.04</v>
       </c>
       <c r="C104" t="n">
-        <v>0.5079016365292793</v>
+        <v>0.09999999999999921</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G104" t="n">
-        <v>0.07181799049392321</v>
+        <v>0.8000000000000006</v>
       </c>
       <c r="H104" t="n">
-        <v>6.696783587524019</v>
+        <v>0.4932760014891795</v>
       </c>
       <c r="I104" t="n">
         <v>490</v>
@@ -6160,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>149.78</v>
+        <v>149.27</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -6182,40 +6170,40 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="B105" t="n">
-        <v>32.43</v>
+        <v>0.04</v>
       </c>
       <c r="C105" t="n">
-        <v>2.757329040020415</v>
+        <v>0.1004999999999993</v>
       </c>
       <c r="D105" t="n">
-        <v>2.76</v>
+        <v>0.1</v>
       </c>
       <c r="E105" t="n">
-        <v>25.72506824438712</v>
+        <v>0.5</v>
       </c>
       <c r="F105" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G105" t="n">
-        <v>2.069035682144603</v>
+        <v>0.002783821232354237</v>
       </c>
       <c r="H105" t="n">
-        <v>98.89878307187891</v>
+        <v>0.4922681195103912</v>
       </c>
       <c r="I105" t="n">
         <v>490</v>
       </c>
       <c r="J105" t="n">
-        <v>2.018342511670998</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
         <v>5</v>
       </c>
       <c r="L105" t="n">
-        <v>527.16</v>
+        <v>147.78</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -6237,40 +6225,40 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B106" t="n">
-        <v>78.72</v>
+        <v>4.85</v>
       </c>
       <c r="C106" t="n">
-        <v>4.323849379334436</v>
+        <v>1.071087270661353</v>
       </c>
       <c r="D106" t="n">
-        <v>4.32</v>
+        <v>1.07</v>
       </c>
       <c r="E106" t="n">
-        <v>41.12875036894425</v>
+        <v>9.850724201486356</v>
       </c>
       <c r="F106" t="n">
-        <v>41.06</v>
+        <v>9.85</v>
       </c>
       <c r="G106" t="n">
-        <v>3.754300367626449</v>
+        <v>0.3094107911240682</v>
       </c>
       <c r="H106" t="n">
-        <v>200.9969856022909</v>
+        <v>21.48674350563927</v>
       </c>
       <c r="I106" t="n">
         <v>490</v>
       </c>
       <c r="J106" t="n">
-        <v>4.101979298005936</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
         <v>10</v>
       </c>
       <c r="L106" t="n">
-        <v>1625.65</v>
+        <v>28.16</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -6292,43 +6280,43 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="B107" t="n">
-        <v>129.38</v>
+        <v>20.05</v>
       </c>
       <c r="C107" t="n">
-        <v>5.623890343842799</v>
+        <v>2.203422135645428</v>
       </c>
       <c r="D107" t="n">
-        <v>5.62</v>
+        <v>2.2</v>
       </c>
       <c r="E107" t="n">
-        <v>56.38412303965085</v>
+        <v>20.4796750917946</v>
       </c>
       <c r="F107" t="n">
-        <v>56.31</v>
+        <v>20.48</v>
       </c>
       <c r="G107" t="n">
-        <v>5.198658495274866</v>
+        <v>1.279014103499845</v>
       </c>
       <c r="H107" t="n">
-        <v>297.7627715455757</v>
+        <v>66.79865237614463</v>
       </c>
       <c r="I107" t="n">
         <v>490</v>
       </c>
       <c r="J107" t="n">
-        <v>6.076791256032157</v>
+        <v>1.363237803594788</v>
       </c>
       <c r="K107" t="n">
         <v>15</v>
       </c>
       <c r="L107" t="n">
-        <v>3479.7</v>
+        <v>125.48</v>
       </c>
       <c r="M107" t="n">
-        <v>815.4948255375007</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
@@ -6347,43 +6335,43 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B108" t="n">
-        <v>177.73</v>
+        <v>51.88</v>
       </c>
       <c r="C108" t="n">
-        <v>6.631391250128899</v>
+        <v>3.585146092434152</v>
       </c>
       <c r="D108" t="n">
-        <v>6.63</v>
+        <v>3.59</v>
       </c>
       <c r="E108" t="n">
-        <v>71.41745621248796</v>
+        <v>34.20404147037087</v>
       </c>
       <c r="F108" t="n">
-        <v>71.34</v>
+        <v>34.2</v>
       </c>
       <c r="G108" t="n">
-        <v>6.50964901211681</v>
+        <v>2.849327363341041</v>
       </c>
       <c r="H108" t="n">
-        <v>383.2601579995216</v>
+        <v>142.6314266390335</v>
       </c>
       <c r="I108" t="n">
         <v>490</v>
       </c>
       <c r="J108" t="n">
-        <v>7.821635877541258</v>
+        <v>2.910845441612929</v>
       </c>
       <c r="K108" t="n">
         <v>20</v>
       </c>
       <c r="L108" t="n">
-        <v>5950.62</v>
+        <v>675.41</v>
       </c>
       <c r="M108" t="n">
-        <v>2028.538170479959</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
@@ -6402,43 +6390,43 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B109" t="n">
-        <v>217.34</v>
+        <v>104.11</v>
       </c>
       <c r="C109" t="n">
-        <v>7.403498835779518</v>
+        <v>5.138212676850372</v>
       </c>
       <c r="D109" t="n">
-        <v>7.39</v>
+        <v>5.14</v>
       </c>
       <c r="E109" t="n">
-        <v>85.12601947469415</v>
+        <v>48.27229194374179</v>
       </c>
       <c r="F109" t="n">
-        <v>85.04000000000001</v>
+        <v>48.27</v>
       </c>
       <c r="G109" t="n">
-        <v>7.526371593722517</v>
+        <v>4.422299974829469</v>
       </c>
       <c r="H109" t="n">
-        <v>448.7255678334397</v>
+        <v>248.3085533506186</v>
       </c>
       <c r="I109" t="n">
         <v>490</v>
       </c>
       <c r="J109" t="n">
-        <v>9.157664649662035</v>
+        <v>5.0675214969514</v>
       </c>
       <c r="K109" t="n">
         <v>25</v>
       </c>
       <c r="L109" t="n">
-        <v>8608.59</v>
+        <v>1968.49</v>
       </c>
       <c r="M109" t="n">
-        <v>3478.963205691998</v>
+        <v>750.3382168803614</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
